--- a/Archivos en excel/Ficha prueba de producto.xlsx
+++ b/Archivos en excel/Ficha prueba de producto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\compras01\Documents\Compra Rafa\BASE DE DATOS DE ITEMS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\controlab-desa\Archivos en excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C46B5BC-E8EF-490D-A3A5-B669E9772752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CEB5A8C-9C1B-4CD7-B003-B4179DB74A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inicio" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -3759,7 +3762,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="166" formatCode="\$#,##0.00;[Red]&quot;($&quot;#,##0.00\);\-"/>
+    <numFmt numFmtId="165" formatCode="\$#,##0.00;[Red]&quot;($&quot;#,##0.00\);\-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -4020,7 +4023,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -4069,6 +4072,56 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -4076,7 +4129,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -4106,19 +4159,19 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -4142,41 +4195,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4226,6 +4244,76 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4493,7 +4581,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -4501,236 +4589,226 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="43"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="56"/>
     </row>
     <row r="2" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
     </row>
     <row r="5" spans="1:8" ht="63.75" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
     </row>
     <row r="6" spans="1:8" ht="93.75" customHeight="1">
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
     </row>
     <row r="7" spans="1:8" ht="63.75" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="40" t="s">
+      <c r="C7" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
     </row>
     <row r="8" spans="1:8" ht="63.75" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
       <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
       <c r="B12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
       <c r="B13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="38" t="s">
+      <c r="C13" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1">
       <c r="B14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
+      <c r="C16" s="63"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="63"/>
+      <c r="G16" s="63"/>
+      <c r="H16" s="63"/>
     </row>
     <row r="17" spans="2:8" ht="39.75" customHeight="1">
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="62"/>
+      <c r="H17" s="62"/>
     </row>
     <row r="18" spans="2:8" ht="39.75" customHeight="1">
-      <c r="B18" s="37" t="s">
+      <c r="B18" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="62"/>
     </row>
     <row r="19" spans="2:8" ht="39.75" customHeight="1">
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="62"/>
     </row>
     <row r="20" spans="2:8" ht="39.75" customHeight="1">
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
     </row>
     <row r="21" spans="2:8" ht="39.75" customHeight="1">
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="C5:H5"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C7:H7"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="C11:H11"/>
     <mergeCell ref="B18:H18"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B20:H20"/>
@@ -4740,6 +4818,16 @@
     <mergeCell ref="C14:H14"/>
     <mergeCell ref="B16:H16"/>
     <mergeCell ref="B17:H17"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="C5:H5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.5"/>
@@ -4753,7 +4841,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -4762,38 +4850,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21.75" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="43"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="56"/>
     </row>
     <row r="2" spans="1:4" ht="25.5" customHeight="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
     </row>
     <row r="5" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
     </row>
     <row r="6" spans="1:4" ht="24" customHeight="1">
       <c r="A6" s="6" t="s">
@@ -4858,12 +4946,12 @@
       <c r="D11" s="8"/>
     </row>
     <row r="13" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="46"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1">
       <c r="A14" s="6" t="s">
@@ -4897,12 +4985,12 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A18" s="46" t="s">
+      <c r="A18" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
+      <c r="B18" s="64"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="64"/>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1">
       <c r="A19" s="6" t="s">
@@ -4961,105 +5049,105 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O113"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <dimension ref="A1:O114"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" style="58" customWidth="1"/>
-    <col min="3" max="3" width="30" style="58" customWidth="1"/>
-    <col min="4" max="4" width="8" style="60" customWidth="1"/>
+    <col min="2" max="2" width="9.90625" style="43" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30" style="43" customWidth="1"/>
+    <col min="4" max="4" width="8" style="45" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="9" style="68" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" customWidth="1"/>
-    <col min="8" max="11" width="9" style="64" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" style="51" customWidth="1"/>
+    <col min="6" max="6" width="9" style="53" customWidth="1"/>
+    <col min="7" max="7" width="21.453125" customWidth="1"/>
+    <col min="8" max="11" width="9" style="49" customWidth="1"/>
+    <col min="12" max="12" width="9.81640625" style="81" customWidth="1"/>
     <col min="13" max="14" width="24" customWidth="1"/>
     <col min="15" max="15" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="26.25" customHeight="1">
-      <c r="A1" s="52" t="s">
+    <row r="1" spans="1:15" s="43" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A1" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="56" t="s">
+      <c r="B1" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="C1" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="37" t="s">
         <v>1088</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="E1" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="37" t="s">
         <v>1094</v>
       </c>
-      <c r="G1" s="52" t="s">
+      <c r="G1" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="H1" s="61" t="s">
+      <c r="H1" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="61" t="s">
+      <c r="I1" s="46" t="s">
         <v>1090</v>
       </c>
-      <c r="J1" s="61" t="s">
+      <c r="J1" s="46" t="s">
         <v>1091</v>
       </c>
-      <c r="K1" s="61" t="s">
+      <c r="K1" s="46" t="s">
         <v>1093</v>
       </c>
-      <c r="L1" s="53" t="s">
+      <c r="L1" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="M1" s="52" t="s">
+      <c r="M1" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="N1" s="52" t="s">
+      <c r="N1" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="O1" s="52" t="s">
+      <c r="O1" s="37" t="s">
         <v>1092</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="19.5" customHeight="1">
+    <row r="2" spans="1:15" s="43" customFormat="1" ht="19.5" customHeight="1">
       <c r="A2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E2" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="67">
+      <c r="F2" s="52">
         <v>1</v>
       </c>
       <c r="G2" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="62">
+      <c r="H2" s="47">
         <v>160</v>
       </c>
-      <c r="I2" s="62">
+      <c r="I2" s="47">
         <v>2</v>
       </c>
-      <c r="J2" s="62">
+      <c r="J2" s="47">
         <v>14</v>
       </c>
-      <c r="K2" s="62">
+      <c r="K2" s="47">
         <f>SUM(I2*J2)</f>
         <v>28</v>
       </c>
-      <c r="L2" s="50">
+      <c r="L2" s="79">
         <v>112</v>
       </c>
       <c r="M2" s="17" t="s">
@@ -5070,42 +5158,42 @@
       </c>
       <c r="O2" s="18"/>
     </row>
-    <row r="3" spans="1:15" ht="26.25" customHeight="1">
+    <row r="3" spans="1:15" s="43" customFormat="1" ht="26.25" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D3" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="67">
+      <c r="F3" s="52">
         <v>1</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="H3" s="62">
+      <c r="H3" s="47">
         <v>272</v>
       </c>
-      <c r="I3" s="62">
-        <v>1</v>
-      </c>
-      <c r="J3" s="62">
+      <c r="I3" s="47">
+        <v>1</v>
+      </c>
+      <c r="J3" s="47">
         <v>60</v>
       </c>
-      <c r="K3" s="62">
-        <f t="shared" ref="K3:K66" si="0">SUM(I3*J3)</f>
+      <c r="K3" s="47">
+        <f t="shared" ref="K3:K57" si="0">SUM(I3*J3)</f>
         <v>60</v>
       </c>
-      <c r="L3" s="50">
+      <c r="L3" s="79">
         <v>190</v>
       </c>
       <c r="M3" s="17" t="s">
@@ -5116,42 +5204,42 @@
       </c>
       <c r="O3" s="18"/>
     </row>
-    <row r="4" spans="1:15" ht="21.75" customHeight="1">
+    <row r="4" spans="1:15" s="43" customFormat="1" ht="21.75" customHeight="1">
       <c r="A4" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="59" t="s">
+      <c r="D4" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F4" s="67">
+      <c r="F4" s="52">
         <v>1</v>
       </c>
       <c r="G4" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="H4" s="62">
+      <c r="H4" s="47">
         <v>728</v>
       </c>
-      <c r="I4" s="62">
+      <c r="I4" s="47">
         <v>4</v>
       </c>
-      <c r="J4" s="62">
+      <c r="J4" s="47">
         <v>40</v>
       </c>
-      <c r="K4" s="62">
+      <c r="K4" s="47">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
-      <c r="L4" s="50">
+      <c r="L4" s="79">
         <v>12.5</v>
       </c>
       <c r="M4" s="17" t="s">
@@ -5162,43 +5250,43 @@
       </c>
       <c r="O4" s="18"/>
     </row>
-    <row r="5" spans="1:15" ht="33.75" customHeight="1">
+    <row r="5" spans="1:15" s="43" customFormat="1" ht="33.75" customHeight="1">
       <c r="A5" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="B5" s="57" t="s">
+      <c r="B5" s="42" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="C5" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="D5" s="59" t="s">
+      <c r="D5" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="67">
+      <c r="F5" s="52">
         <v>1</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="H5" s="62">
+      <c r="H5" s="47">
         <v>942</v>
       </c>
-      <c r="I5" s="62">
+      <c r="I5" s="47">
         <v>2</v>
       </c>
-      <c r="J5" s="62">
+      <c r="J5" s="47">
         <f>((4*35)/2)+18</f>
         <v>88</v>
       </c>
-      <c r="K5" s="62">
+      <c r="K5" s="47">
         <f t="shared" si="0"/>
         <v>176</v>
       </c>
-      <c r="L5" s="50">
+      <c r="L5" s="79">
         <v>16.5</v>
       </c>
       <c r="M5" s="17" t="s">
@@ -5209,43 +5297,43 @@
       </c>
       <c r="O5" s="18"/>
     </row>
-    <row r="6" spans="1:15" ht="26.25" customHeight="1">
+    <row r="6" spans="1:15" s="43" customFormat="1" ht="26.25" customHeight="1">
       <c r="A6" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="59" t="s">
+      <c r="D6" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F6" s="67">
+      <c r="F6" s="52">
         <v>1</v>
       </c>
       <c r="G6" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="H6" s="62">
+      <c r="H6" s="47">
         <v>942</v>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="47">
         <v>2</v>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="47">
         <f>((4*35)/2)+18</f>
         <v>88</v>
       </c>
-      <c r="K6" s="62">
+      <c r="K6" s="47">
         <f t="shared" si="0"/>
         <v>176</v>
       </c>
-      <c r="L6" s="50">
+      <c r="L6" s="79">
         <v>23</v>
       </c>
       <c r="M6" s="17" t="s">
@@ -5256,42 +5344,42 @@
       </c>
       <c r="O6" s="18"/>
     </row>
-    <row r="7" spans="1:15" ht="28.5" customHeight="1">
+    <row r="7" spans="1:15" s="43" customFormat="1" ht="28.5" customHeight="1">
       <c r="A7" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="57" t="s">
+      <c r="B7" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="59" t="s">
+      <c r="D7" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F7" s="67">
+      <c r="F7" s="52">
         <v>1</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="H7" s="62">
+      <c r="H7" s="47">
         <v>242</v>
       </c>
-      <c r="I7" s="62">
-        <v>1</v>
-      </c>
-      <c r="J7" s="62">
+      <c r="I7" s="47">
+        <v>1</v>
+      </c>
+      <c r="J7" s="47">
         <v>48</v>
       </c>
-      <c r="K7" s="62">
+      <c r="K7" s="47">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="L7" s="50">
+      <c r="L7" s="79">
         <v>39.5</v>
       </c>
       <c r="M7" s="17" t="s">
@@ -5302,43 +5390,43 @@
       </c>
       <c r="O7" s="18"/>
     </row>
-    <row r="8" spans="1:15" ht="23.25" customHeight="1">
+    <row r="8" spans="1:15" s="43" customFormat="1" ht="23.25" customHeight="1">
       <c r="A8" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="55" t="s">
+      <c r="C8" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="59" t="s">
+      <c r="D8" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="67">
+      <c r="F8" s="52">
         <v>1</v>
       </c>
       <c r="G8" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="H8" s="62">
+      <c r="H8" s="47">
         <v>145</v>
       </c>
-      <c r="I8" s="62">
-        <v>1</v>
-      </c>
-      <c r="J8" s="62">
+      <c r="I8" s="47">
+        <v>1</v>
+      </c>
+      <c r="J8" s="47">
         <f>35+12</f>
         <v>47</v>
       </c>
-      <c r="K8" s="62">
+      <c r="K8" s="47">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="L8" s="50">
+      <c r="L8" s="79">
         <v>65</v>
       </c>
       <c r="M8" s="17" t="s">
@@ -5349,43 +5437,43 @@
       </c>
       <c r="O8" s="18"/>
     </row>
-    <row r="9" spans="1:15" ht="17.25" customHeight="1">
+    <row r="9" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A9" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="C9" s="55" t="s">
+      <c r="C9" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="D9" s="59" t="s">
+      <c r="D9" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="67">
+      <c r="F9" s="52">
         <v>1</v>
       </c>
       <c r="G9" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="H9" s="62">
+      <c r="H9" s="47">
         <v>145</v>
       </c>
-      <c r="I9" s="62">
-        <v>1</v>
-      </c>
-      <c r="J9" s="62">
+      <c r="I9" s="47">
+        <v>1</v>
+      </c>
+      <c r="J9" s="47">
         <f>35+12</f>
         <v>47</v>
       </c>
-      <c r="K9" s="62">
+      <c r="K9" s="47">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="L9" s="50">
+      <c r="L9" s="79">
         <v>65</v>
       </c>
       <c r="M9" s="17" t="s">
@@ -5396,43 +5484,43 @@
       </c>
       <c r="O9" s="18"/>
     </row>
-    <row r="10" spans="1:15" ht="17.25" customHeight="1">
+    <row r="10" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A10" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="B10" s="57" t="s">
+      <c r="B10" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="D10" s="59" t="s">
+      <c r="D10" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F10" s="67">
+      <c r="F10" s="52">
         <v>1</v>
       </c>
       <c r="G10" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="H10" s="62">
+      <c r="H10" s="47">
         <v>241</v>
       </c>
-      <c r="I10" s="62">
-        <v>1</v>
-      </c>
-      <c r="J10" s="62">
+      <c r="I10" s="47">
+        <v>1</v>
+      </c>
+      <c r="J10" s="47">
         <f>40+40</f>
         <v>80</v>
       </c>
-      <c r="K10" s="62">
+      <c r="K10" s="47">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="L10" s="50">
+      <c r="L10" s="79">
         <v>195</v>
       </c>
       <c r="M10" s="17" t="s">
@@ -5443,43 +5531,43 @@
       </c>
       <c r="O10" s="18"/>
     </row>
-    <row r="11" spans="1:15" ht="17.25" customHeight="1">
+    <row r="11" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A11" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="B11" s="57" t="s">
+      <c r="B11" s="42" t="s">
         <v>107</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="C11" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="D11" s="59" t="s">
+      <c r="D11" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="67">
+      <c r="F11" s="52">
         <v>1</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="H11" s="62">
+      <c r="H11" s="47">
         <v>942</v>
       </c>
-      <c r="I11" s="62">
+      <c r="I11" s="47">
         <v>2</v>
       </c>
-      <c r="J11" s="62">
+      <c r="J11" s="47">
         <f>((4*35)/2)+18</f>
         <v>88</v>
       </c>
-      <c r="K11" s="62">
+      <c r="K11" s="47">
         <f t="shared" si="0"/>
         <v>176</v>
       </c>
-      <c r="L11" s="50">
+      <c r="L11" s="79">
         <v>23</v>
       </c>
       <c r="M11" s="17" t="s">
@@ -5490,43 +5578,43 @@
       </c>
       <c r="O11" s="18"/>
     </row>
-    <row r="12" spans="1:15" ht="17.25" customHeight="1">
+    <row r="12" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A12" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="B12" s="57" t="s">
+      <c r="B12" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="55" t="s">
+      <c r="C12" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="D12" s="59" t="s">
+      <c r="D12" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F12" s="67">
+      <c r="F12" s="52">
         <v>1</v>
       </c>
       <c r="G12" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="H12" s="62">
+      <c r="H12" s="47">
         <v>227</v>
       </c>
-      <c r="I12" s="62">
-        <v>1</v>
-      </c>
-      <c r="J12" s="62">
+      <c r="I12" s="47">
+        <v>1</v>
+      </c>
+      <c r="J12" s="47">
         <f>40+12</f>
         <v>52</v>
       </c>
-      <c r="K12" s="62">
+      <c r="K12" s="47">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="L12" s="50">
+      <c r="L12" s="79">
         <v>350</v>
       </c>
       <c r="M12" s="17" t="s">
@@ -5537,43 +5625,43 @@
       </c>
       <c r="O12" s="18"/>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1">
+    <row r="13" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="C13" s="55" t="s">
+      <c r="C13" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="D13" s="59" t="s">
+      <c r="D13" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F13" s="67">
+      <c r="F13" s="52">
         <v>1</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="H13" s="62">
+      <c r="H13" s="47">
         <v>220</v>
       </c>
-      <c r="I13" s="62">
-        <v>1</v>
-      </c>
-      <c r="J13" s="62">
+      <c r="I13" s="47">
+        <v>1</v>
+      </c>
+      <c r="J13" s="47">
         <f>36+18</f>
         <v>54</v>
       </c>
-      <c r="K13" s="62">
+      <c r="K13" s="47">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="L13" s="50">
+      <c r="L13" s="79">
         <v>55</v>
       </c>
       <c r="M13" s="17" t="s">
@@ -5584,43 +5672,43 @@
       </c>
       <c r="O13" s="18"/>
     </row>
-    <row r="14" spans="1:15" ht="23.25" customHeight="1">
+    <row r="14" spans="1:15" s="43" customFormat="1" ht="23.25" customHeight="1">
       <c r="A14" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="C14" s="55" t="s">
+      <c r="C14" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="D14" s="59" t="s">
+      <c r="D14" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="67">
+      <c r="F14" s="52">
         <v>1</v>
       </c>
       <c r="G14" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="H14" s="62">
+      <c r="H14" s="47">
         <v>207</v>
       </c>
-      <c r="I14" s="62">
-        <v>1</v>
-      </c>
-      <c r="J14" s="62">
+      <c r="I14" s="47">
+        <v>1</v>
+      </c>
+      <c r="J14" s="47">
         <f>40+15</f>
         <v>55</v>
       </c>
-      <c r="K14" s="62">
+      <c r="K14" s="47">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="L14" s="50">
+      <c r="L14" s="79">
         <v>62</v>
       </c>
       <c r="M14" s="17" t="s">
@@ -5631,42 +5719,42 @@
       </c>
       <c r="O14" s="18"/>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1">
+    <row r="15" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="B15" s="57" t="s">
+      <c r="B15" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="55" t="s">
+      <c r="C15" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="D15" s="59" t="s">
+      <c r="D15" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F15" s="67">
+      <c r="F15" s="52">
         <v>1</v>
       </c>
       <c r="G15" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="H15" s="62">
+      <c r="H15" s="47">
         <v>728</v>
       </c>
-      <c r="I15" s="62">
+      <c r="I15" s="47">
         <v>4</v>
       </c>
-      <c r="J15" s="62">
+      <c r="J15" s="47">
         <v>40</v>
       </c>
-      <c r="K15" s="62">
+      <c r="K15" s="47">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
-      <c r="L15" s="50">
+      <c r="L15" s="79">
         <v>17</v>
       </c>
       <c r="M15" s="17" t="s">
@@ -5677,42 +5765,42 @@
       </c>
       <c r="O15" s="18"/>
     </row>
-    <row r="16" spans="1:15" ht="36" customHeight="1">
+    <row r="16" spans="1:15" s="43" customFormat="1" ht="36" customHeight="1">
       <c r="A16" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="B16" s="57" t="s">
+      <c r="B16" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="C16" s="55" t="s">
+      <c r="C16" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="D16" s="59" t="s">
+      <c r="D16" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F16" s="67">
+      <c r="F16" s="52">
         <v>1</v>
       </c>
       <c r="G16" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="H16" s="62">
+      <c r="H16" s="47">
         <v>483</v>
       </c>
-      <c r="I16" s="62">
-        <v>1</v>
-      </c>
-      <c r="J16" s="62">
+      <c r="I16" s="47">
+        <v>1</v>
+      </c>
+      <c r="J16" s="47">
         <v>104</v>
       </c>
-      <c r="K16" s="62">
+      <c r="K16" s="47">
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
-      <c r="L16" s="50">
+      <c r="L16" s="79">
         <v>122.5</v>
       </c>
       <c r="M16" s="17" t="s">
@@ -5723,43 +5811,43 @@
       </c>
       <c r="O16" s="18"/>
     </row>
-    <row r="17" spans="1:15" ht="17.25" customHeight="1">
+    <row r="17" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A17" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="B17" s="57" t="s">
+      <c r="B17" s="42" t="s">
         <v>131</v>
       </c>
-      <c r="C17" s="55" t="s">
+      <c r="C17" s="40" t="s">
         <v>132</v>
       </c>
-      <c r="D17" s="59" t="s">
+      <c r="D17" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F17" s="67">
+      <c r="F17" s="52">
         <v>1</v>
       </c>
       <c r="G17" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="H17" s="62">
+      <c r="H17" s="47">
         <v>471</v>
       </c>
-      <c r="I17" s="62">
-        <v>1</v>
-      </c>
-      <c r="J17" s="62">
+      <c r="I17" s="47">
+        <v>1</v>
+      </c>
+      <c r="J17" s="47">
         <f t="shared" ref="J17:J18" si="1">35+18</f>
         <v>53</v>
       </c>
-      <c r="K17" s="62">
+      <c r="K17" s="47">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="L17" s="50">
+      <c r="L17" s="79">
         <v>58</v>
       </c>
       <c r="M17" s="17" t="s">
@@ -5770,43 +5858,43 @@
       </c>
       <c r="O17" s="18"/>
     </row>
-    <row r="18" spans="1:15" ht="17.25" customHeight="1">
+    <row r="18" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A18" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="B18" s="57" t="s">
+      <c r="B18" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="C18" s="55" t="s">
+      <c r="C18" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="D18" s="59" t="s">
+      <c r="D18" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F18" s="67">
+      <c r="F18" s="52">
         <v>1</v>
       </c>
       <c r="G18" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="H18" s="62">
+      <c r="H18" s="47">
         <v>471</v>
       </c>
-      <c r="I18" s="62">
-        <v>1</v>
-      </c>
-      <c r="J18" s="62">
+      <c r="I18" s="47">
+        <v>1</v>
+      </c>
+      <c r="J18" s="47">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="K18" s="62">
+      <c r="K18" s="47">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="L18" s="50">
+      <c r="L18" s="79">
         <v>131</v>
       </c>
       <c r="M18" s="17" t="s">
@@ -5817,43 +5905,43 @@
       </c>
       <c r="O18" s="18"/>
     </row>
-    <row r="19" spans="1:15" ht="28.5" customHeight="1">
+    <row r="19" spans="1:15" s="43" customFormat="1" ht="28.5" customHeight="1">
       <c r="A19" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="B19" s="57" t="s">
+      <c r="B19" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="C19" s="55" t="s">
+      <c r="C19" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="D19" s="59" t="s">
+      <c r="D19" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="67">
+      <c r="F19" s="52">
         <v>1</v>
       </c>
       <c r="G19" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="H19" s="62">
+      <c r="H19" s="47">
         <v>150</v>
       </c>
-      <c r="I19" s="62">
-        <v>1</v>
-      </c>
-      <c r="J19" s="65">
+      <c r="I19" s="47">
+        <v>1</v>
+      </c>
+      <c r="J19" s="50">
         <f>40+5+1.5</f>
         <v>46.5</v>
       </c>
-      <c r="K19" s="62">
+      <c r="K19" s="47">
         <f t="shared" si="0"/>
         <v>46.5</v>
       </c>
-      <c r="L19" s="50">
+      <c r="L19" s="79">
         <v>60</v>
       </c>
       <c r="M19" s="17" t="s">
@@ -5864,42 +5952,42 @@
       </c>
       <c r="O19" s="18"/>
     </row>
-    <row r="20" spans="1:15" ht="17.25" customHeight="1">
+    <row r="20" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A20" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="B20" s="57" t="s">
+      <c r="B20" s="42" t="s">
         <v>143</v>
       </c>
-      <c r="C20" s="55" t="s">
+      <c r="C20" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="D20" s="59" t="s">
+      <c r="D20" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F20" s="67">
+      <c r="F20" s="52">
         <v>1</v>
       </c>
       <c r="G20" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="H20" s="62">
+      <c r="H20" s="47">
         <v>780</v>
       </c>
-      <c r="I20" s="62">
+      <c r="I20" s="47">
         <v>3</v>
       </c>
-      <c r="J20" s="62">
+      <c r="J20" s="47">
         <v>70</v>
       </c>
-      <c r="K20" s="62">
+      <c r="K20" s="47">
         <f t="shared" si="0"/>
         <v>210</v>
       </c>
-      <c r="L20" s="50">
+      <c r="L20" s="79">
         <v>16</v>
       </c>
       <c r="M20" s="17" t="s">
@@ -5910,42 +5998,42 @@
       </c>
       <c r="O20" s="18"/>
     </row>
-    <row r="21" spans="1:15" ht="17.25" customHeight="1">
+    <row r="21" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A21" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="B21" s="57" t="s">
+      <c r="B21" s="42" t="s">
         <v>147</v>
       </c>
-      <c r="C21" s="55" t="s">
+      <c r="C21" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="59" t="s">
+      <c r="D21" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="67">
+      <c r="F21" s="52">
         <v>1</v>
       </c>
       <c r="G21" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="H21" s="62">
+      <c r="H21" s="47">
         <v>188</v>
       </c>
-      <c r="I21" s="62">
-        <v>1</v>
-      </c>
-      <c r="J21" s="62">
+      <c r="I21" s="47">
+        <v>1</v>
+      </c>
+      <c r="J21" s="47">
         <v>50</v>
       </c>
-      <c r="K21" s="62">
+      <c r="K21" s="47">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="L21" s="50">
+      <c r="L21" s="79">
         <v>60.5</v>
       </c>
       <c r="M21" s="17" t="s">
@@ -5956,43 +6044,43 @@
       </c>
       <c r="O21" s="18"/>
     </row>
-    <row r="22" spans="1:15" ht="17.25" customHeight="1">
+    <row r="22" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A22" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="B22" s="57" t="s">
+      <c r="B22" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="C22" s="55" t="s">
+      <c r="C22" s="40" t="s">
         <v>153</v>
       </c>
-      <c r="D22" s="59" t="s">
+      <c r="D22" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="67">
+      <c r="F22" s="52">
         <v>1</v>
       </c>
       <c r="G22" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="H22" s="62">
+      <c r="H22" s="47">
         <v>300</v>
       </c>
-      <c r="I22" s="62">
-        <v>1</v>
-      </c>
-      <c r="J22" s="62">
+      <c r="I22" s="47">
+        <v>1</v>
+      </c>
+      <c r="J22" s="47">
         <f>40+12</f>
         <v>52</v>
       </c>
-      <c r="K22" s="62">
+      <c r="K22" s="47">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="L22" s="50">
+      <c r="L22" s="79">
         <v>288</v>
       </c>
       <c r="M22" s="17" t="s">
@@ -6003,43 +6091,43 @@
       </c>
       <c r="O22" s="18"/>
     </row>
-    <row r="23" spans="1:15" ht="17.25" customHeight="1">
+    <row r="23" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A23" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="B23" s="57" t="s">
+      <c r="B23" s="42" t="s">
         <v>157</v>
       </c>
-      <c r="C23" s="55" t="s">
+      <c r="C23" s="40" t="s">
         <v>158</v>
       </c>
-      <c r="D23" s="59" t="s">
+      <c r="D23" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F23" s="67">
+      <c r="F23" s="52">
         <v>1</v>
       </c>
       <c r="G23" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="H23" s="62">
+      <c r="H23" s="47">
         <v>411</v>
       </c>
-      <c r="I23" s="62">
+      <c r="I23" s="47">
         <v>4</v>
       </c>
-      <c r="J23" s="62">
+      <c r="J23" s="47">
         <f>((4*40)/2)+20</f>
         <v>100</v>
       </c>
-      <c r="K23" s="62">
+      <c r="K23" s="47">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="L23" s="50">
+      <c r="L23" s="79">
         <v>13.5</v>
       </c>
       <c r="M23" s="17" t="s">
@@ -6050,43 +6138,43 @@
       </c>
       <c r="O23" s="18"/>
     </row>
-    <row r="24" spans="1:15" ht="24" customHeight="1">
+    <row r="24" spans="1:15" s="43" customFormat="1" ht="24" customHeight="1">
       <c r="A24" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="B24" s="57" t="s">
+      <c r="B24" s="42" t="s">
         <v>161</v>
       </c>
-      <c r="C24" s="55" t="s">
+      <c r="C24" s="40" t="s">
         <v>162</v>
       </c>
-      <c r="D24" s="59" t="s">
+      <c r="D24" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F24" s="67">
+      <c r="F24" s="52">
         <v>1</v>
       </c>
       <c r="G24" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="H24" s="62">
+      <c r="H24" s="47">
         <v>104</v>
       </c>
-      <c r="I24" s="62">
+      <c r="I24" s="47">
         <v>2</v>
       </c>
-      <c r="J24" s="62">
+      <c r="J24" s="47">
         <f>8+4+1</f>
         <v>13</v>
       </c>
-      <c r="K24" s="62">
+      <c r="K24" s="47">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="L24" s="50">
+      <c r="L24" s="79">
         <v>174.5</v>
       </c>
       <c r="M24" s="17" t="s">
@@ -6097,43 +6185,43 @@
       </c>
       <c r="O24" s="18"/>
     </row>
-    <row r="25" spans="1:15" ht="36" customHeight="1">
+    <row r="25" spans="1:15" s="43" customFormat="1" ht="36" customHeight="1">
       <c r="A25" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="B25" s="57" t="s">
+      <c r="B25" s="42" t="s">
         <v>165</v>
       </c>
-      <c r="C25" s="55" t="s">
+      <c r="C25" s="40" t="s">
         <v>166</v>
       </c>
-      <c r="D25" s="59" t="s">
+      <c r="D25" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F25" s="67">
+      <c r="F25" s="52">
         <v>1</v>
       </c>
       <c r="G25" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="H25" s="62">
+      <c r="H25" s="47">
         <v>483</v>
       </c>
-      <c r="I25" s="62">
-        <v>1</v>
-      </c>
-      <c r="J25" s="65">
+      <c r="I25" s="47">
+        <v>1</v>
+      </c>
+      <c r="J25" s="50">
         <f>40+16+5+1.5</f>
         <v>62.5</v>
       </c>
-      <c r="K25" s="62">
+      <c r="K25" s="47">
         <f t="shared" si="0"/>
         <v>62.5</v>
       </c>
-      <c r="L25" s="50">
+      <c r="L25" s="79">
         <v>51.5</v>
       </c>
       <c r="M25" s="17" t="s">
@@ -6144,43 +6232,43 @@
       </c>
       <c r="O25" s="18"/>
     </row>
-    <row r="26" spans="1:15" ht="30" customHeight="1">
+    <row r="26" spans="1:15" s="43" customFormat="1" ht="30" customHeight="1">
       <c r="A26" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="B26" s="57" t="s">
+      <c r="B26" s="42" t="s">
         <v>169</v>
       </c>
-      <c r="C26" s="55" t="s">
+      <c r="C26" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="D26" s="59" t="s">
+      <c r="D26" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F26" s="67">
+      <c r="F26" s="52">
         <v>1</v>
       </c>
       <c r="G26" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="H26" s="62">
+      <c r="H26" s="47">
         <v>260</v>
       </c>
-      <c r="I26" s="62">
+      <c r="I26" s="47">
         <v>2</v>
       </c>
-      <c r="J26" s="62">
+      <c r="J26" s="47">
         <f>28+10</f>
         <v>38</v>
       </c>
-      <c r="K26" s="62">
+      <c r="K26" s="47">
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="L26" s="50">
+      <c r="L26" s="79">
         <v>360</v>
       </c>
       <c r="M26" s="17" t="s">
@@ -6191,43 +6279,43 @@
       </c>
       <c r="O26" s="18"/>
     </row>
-    <row r="27" spans="1:15" ht="17.25" customHeight="1">
+    <row r="27" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A27" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="B27" s="57" t="s">
+      <c r="B27" s="42" t="s">
         <v>174</v>
       </c>
-      <c r="C27" s="55" t="s">
+      <c r="C27" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="D27" s="59" t="s">
+      <c r="D27" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F27" s="67">
+      <c r="F27" s="52">
         <v>1</v>
       </c>
       <c r="G27" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="H27" s="62">
+      <c r="H27" s="47">
         <v>241</v>
       </c>
-      <c r="I27" s="62">
-        <v>1</v>
-      </c>
-      <c r="J27" s="62">
+      <c r="I27" s="47">
+        <v>1</v>
+      </c>
+      <c r="J27" s="47">
         <f>40+40</f>
         <v>80</v>
       </c>
-      <c r="K27" s="62">
+      <c r="K27" s="47">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="L27" s="50">
+      <c r="L27" s="79">
         <v>240</v>
       </c>
       <c r="M27" s="17" t="s">
@@ -6238,43 +6326,43 @@
       </c>
       <c r="O27" s="18"/>
     </row>
-    <row r="28" spans="1:15" ht="36" customHeight="1">
+    <row r="28" spans="1:15" s="43" customFormat="1" ht="36" customHeight="1">
       <c r="A28" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="B28" s="57" t="s">
+      <c r="B28" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="C28" s="55" t="s">
+      <c r="C28" s="40" t="s">
         <v>178</v>
       </c>
-      <c r="D28" s="59" t="s">
+      <c r="D28" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F28" s="67">
+      <c r="F28" s="52">
         <v>1</v>
       </c>
       <c r="G28" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="H28" s="62">
+      <c r="H28" s="47">
         <v>385</v>
       </c>
-      <c r="I28" s="62">
-        <v>1</v>
-      </c>
-      <c r="J28" s="62">
+      <c r="I28" s="47">
+        <v>1</v>
+      </c>
+      <c r="J28" s="47">
         <f>30+15+1.5+1</f>
         <v>47.5</v>
       </c>
-      <c r="K28" s="62">
+      <c r="K28" s="47">
         <f t="shared" si="0"/>
         <v>47.5</v>
       </c>
-      <c r="L28" s="50">
+      <c r="L28" s="79">
         <v>171</v>
       </c>
       <c r="M28" s="17" t="s">
@@ -6285,43 +6373,43 @@
       </c>
       <c r="O28" s="18"/>
     </row>
-    <row r="29" spans="1:15" ht="17.25" customHeight="1">
+    <row r="29" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A29" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="B29" s="57" t="s">
+      <c r="B29" s="42" t="s">
         <v>181</v>
       </c>
-      <c r="C29" s="55" t="s">
+      <c r="C29" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="D29" s="59" t="s">
+      <c r="D29" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F29" s="67">
+      <c r="F29" s="52">
         <v>1</v>
       </c>
       <c r="G29" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="H29" s="62">
+      <c r="H29" s="47">
         <v>942</v>
       </c>
-      <c r="I29" s="62">
+      <c r="I29" s="47">
         <v>2</v>
       </c>
-      <c r="J29" s="62">
+      <c r="J29" s="47">
         <f>((4*35)/2)+18</f>
         <v>88</v>
       </c>
-      <c r="K29" s="62">
+      <c r="K29" s="47">
         <f t="shared" si="0"/>
         <v>176</v>
       </c>
-      <c r="L29" s="50">
+      <c r="L29" s="79">
         <v>35.5</v>
       </c>
       <c r="M29" s="17" t="s">
@@ -6332,43 +6420,43 @@
       </c>
       <c r="O29" s="18"/>
     </row>
-    <row r="30" spans="1:15" ht="17.25" customHeight="1">
+    <row r="30" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A30" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="B30" s="57" t="s">
+      <c r="B30" s="42" t="s">
         <v>184</v>
       </c>
-      <c r="C30" s="55" t="s">
+      <c r="C30" s="40" t="s">
         <v>185</v>
       </c>
-      <c r="D30" s="59" t="s">
+      <c r="D30" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F30" s="67">
+      <c r="F30" s="52">
         <v>1</v>
       </c>
       <c r="G30" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="H30" s="62">
+      <c r="H30" s="47">
         <v>822</v>
       </c>
-      <c r="I30" s="62">
+      <c r="I30" s="47">
         <v>2</v>
       </c>
-      <c r="J30" s="62">
+      <c r="J30" s="47">
         <f>40+20</f>
         <v>60</v>
       </c>
-      <c r="K30" s="62">
+      <c r="K30" s="47">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="L30" s="50">
+      <c r="L30" s="79">
         <v>17.5</v>
       </c>
       <c r="M30" s="17" t="s">
@@ -6379,43 +6467,43 @@
       </c>
       <c r="O30" s="18"/>
     </row>
-    <row r="31" spans="1:15" ht="25.5" customHeight="1">
+    <row r="31" spans="1:15" s="43" customFormat="1" ht="25.5" customHeight="1">
       <c r="A31" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="B31" s="57" t="s">
+      <c r="B31" s="42" t="s">
         <v>188</v>
       </c>
-      <c r="C31" s="55" t="s">
+      <c r="C31" s="40" t="s">
         <v>189</v>
       </c>
-      <c r="D31" s="59" t="s">
+      <c r="D31" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F31" s="67">
+      <c r="F31" s="52">
         <v>1</v>
       </c>
       <c r="G31" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="H31" s="62">
+      <c r="H31" s="47">
         <v>168</v>
       </c>
-      <c r="I31" s="62">
+      <c r="I31" s="47">
         <v>2</v>
       </c>
-      <c r="J31" s="62">
+      <c r="J31" s="47">
         <f>12+5</f>
         <v>17</v>
       </c>
-      <c r="K31" s="62">
+      <c r="K31" s="47">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="L31" s="50">
+      <c r="L31" s="79">
         <v>100</v>
       </c>
       <c r="M31" s="17" t="s">
@@ -6426,43 +6514,43 @@
       </c>
       <c r="O31" s="18"/>
     </row>
-    <row r="32" spans="1:15" ht="36" customHeight="1">
+    <row r="32" spans="1:15" s="43" customFormat="1" ht="36" customHeight="1">
       <c r="A32" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="B32" s="57" t="s">
+      <c r="B32" s="42" t="s">
         <v>192</v>
       </c>
-      <c r="C32" s="55" t="s">
+      <c r="C32" s="40" t="s">
         <v>193</v>
       </c>
-      <c r="D32" s="59" t="s">
+      <c r="D32" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="67">
-        <v>1</v>
-      </c>
-      <c r="G32" s="66" t="s">
+      <c r="F32" s="52">
+        <v>1</v>
+      </c>
+      <c r="G32" s="51" t="s">
         <v>194</v>
       </c>
-      <c r="H32" s="62">
+      <c r="H32" s="47">
         <v>300</v>
       </c>
-      <c r="I32" s="62">
-        <v>1</v>
-      </c>
-      <c r="J32" s="62">
+      <c r="I32" s="47">
+        <v>1</v>
+      </c>
+      <c r="J32" s="47">
         <f>40+15</f>
         <v>55</v>
       </c>
-      <c r="K32" s="62">
+      <c r="K32" s="47">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="L32" s="50">
+      <c r="L32" s="79">
         <v>400</v>
       </c>
       <c r="M32" s="17" t="s">
@@ -6473,43 +6561,43 @@
       </c>
       <c r="O32" s="18"/>
     </row>
-    <row r="33" spans="1:15" ht="17.25" customHeight="1">
+    <row r="33" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A33" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="B33" s="57" t="s">
+      <c r="B33" s="42" t="s">
         <v>198</v>
       </c>
-      <c r="C33" s="55" t="s">
+      <c r="C33" s="40" t="s">
         <v>199</v>
       </c>
-      <c r="D33" s="59" t="s">
+      <c r="D33" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F33" s="67">
+      <c r="F33" s="52">
         <v>1</v>
       </c>
       <c r="G33" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="H33" s="62">
+      <c r="H33" s="47">
         <v>942</v>
       </c>
-      <c r="I33" s="62">
+      <c r="I33" s="47">
         <v>4</v>
       </c>
-      <c r="J33" s="62">
+      <c r="J33" s="47">
         <f>((4*35)/2)+18</f>
         <v>88</v>
       </c>
-      <c r="K33" s="62">
+      <c r="K33" s="47">
         <f t="shared" si="0"/>
         <v>352</v>
       </c>
-      <c r="L33" s="50">
+      <c r="L33" s="79">
         <v>43</v>
       </c>
       <c r="M33" s="17" t="s">
@@ -6520,43 +6608,43 @@
       </c>
       <c r="O33" s="18"/>
     </row>
-    <row r="34" spans="1:15" ht="17.25" customHeight="1">
+    <row r="34" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A34" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="B34" s="57" t="s">
+      <c r="B34" s="42" t="s">
         <v>201</v>
       </c>
-      <c r="C34" s="55" t="s">
+      <c r="C34" s="40" t="s">
         <v>202</v>
       </c>
-      <c r="D34" s="59" t="s">
+      <c r="D34" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F34" s="67">
+      <c r="F34" s="52">
         <v>1</v>
       </c>
       <c r="G34" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="H34" s="62">
+      <c r="H34" s="47">
         <v>227</v>
       </c>
-      <c r="I34" s="62">
-        <v>1</v>
-      </c>
-      <c r="J34" s="62">
+      <c r="I34" s="47">
+        <v>1</v>
+      </c>
+      <c r="J34" s="47">
         <f>40+14</f>
         <v>54</v>
       </c>
-      <c r="K34" s="62">
+      <c r="K34" s="47">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="L34" s="50">
+      <c r="L34" s="79">
         <v>74.5</v>
       </c>
       <c r="M34" s="17" t="s">
@@ -6567,43 +6655,43 @@
       </c>
       <c r="O34" s="18"/>
     </row>
-    <row r="35" spans="1:15" ht="17.25" customHeight="1">
+    <row r="35" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A35" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="B35" s="57" t="s">
+      <c r="B35" s="42" t="s">
         <v>205</v>
       </c>
-      <c r="C35" s="55" t="s">
+      <c r="C35" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="D35" s="59" t="s">
+      <c r="D35" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="67">
+      <c r="F35" s="52">
         <v>1</v>
       </c>
       <c r="G35" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="H35" s="62">
+      <c r="H35" s="47">
         <v>220</v>
       </c>
-      <c r="I35" s="62">
-        <v>1</v>
-      </c>
-      <c r="J35" s="62">
+      <c r="I35" s="47">
+        <v>1</v>
+      </c>
+      <c r="J35" s="47">
         <f>36+18</f>
         <v>54</v>
       </c>
-      <c r="K35" s="62">
+      <c r="K35" s="47">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="L35" s="50">
+      <c r="L35" s="79">
         <v>107</v>
       </c>
       <c r="M35" s="17" t="s">
@@ -6614,43 +6702,43 @@
       </c>
       <c r="O35" s="18"/>
     </row>
-    <row r="36" spans="1:15" ht="17.25" customHeight="1">
+    <row r="36" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A36" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="B36" s="57" t="s">
+      <c r="B36" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="C36" s="55" t="s">
+      <c r="C36" s="40" t="s">
         <v>210</v>
       </c>
-      <c r="D36" s="59" t="s">
+      <c r="D36" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F36" s="67">
+      <c r="F36" s="52">
         <v>1</v>
       </c>
       <c r="G36" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="H36" s="62">
+      <c r="H36" s="47">
         <v>220</v>
       </c>
-      <c r="I36" s="62">
-        <v>1</v>
-      </c>
-      <c r="J36" s="62">
+      <c r="I36" s="47">
+        <v>1</v>
+      </c>
+      <c r="J36" s="47">
         <f>36+18</f>
         <v>54</v>
       </c>
-      <c r="K36" s="62">
+      <c r="K36" s="47">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="L36" s="50">
+      <c r="L36" s="79">
         <v>107</v>
       </c>
       <c r="M36" s="17" t="s">
@@ -6661,43 +6749,43 @@
       </c>
       <c r="O36" s="18"/>
     </row>
-    <row r="37" spans="1:15" ht="17.25" customHeight="1">
+    <row r="37" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A37" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="B37" s="57" t="s">
+      <c r="B37" s="42" t="s">
         <v>212</v>
       </c>
-      <c r="C37" s="55" t="s">
+      <c r="C37" s="40" t="s">
         <v>213</v>
       </c>
-      <c r="D37" s="59" t="s">
+      <c r="D37" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F37" s="67">
+      <c r="F37" s="52">
         <v>1</v>
       </c>
       <c r="G37" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="H37" s="62">
+      <c r="H37" s="47">
         <v>212</v>
       </c>
-      <c r="I37" s="62">
-        <v>1</v>
-      </c>
-      <c r="J37" s="62">
+      <c r="I37" s="47">
+        <v>1</v>
+      </c>
+      <c r="J37" s="47">
         <f>40+10</f>
         <v>50</v>
       </c>
-      <c r="K37" s="62">
+      <c r="K37" s="47">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="L37" s="50">
+      <c r="L37" s="79">
         <v>100</v>
       </c>
       <c r="M37" s="17" t="s">
@@ -6708,43 +6796,43 @@
       </c>
       <c r="O37" s="18"/>
     </row>
-    <row r="38" spans="1:15" ht="17.25" customHeight="1">
+    <row r="38" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A38" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="B38" s="57" t="s">
+      <c r="B38" s="42" t="s">
         <v>215</v>
       </c>
-      <c r="C38" s="55" t="s">
+      <c r="C38" s="40" t="s">
         <v>216</v>
       </c>
-      <c r="D38" s="59" t="s">
+      <c r="D38" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F38" s="67">
+      <c r="F38" s="52">
         <v>1</v>
       </c>
       <c r="G38" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="H38" s="62">
+      <c r="H38" s="47">
         <v>942</v>
       </c>
-      <c r="I38" s="62">
+      <c r="I38" s="47">
         <v>4</v>
       </c>
-      <c r="J38" s="62">
+      <c r="J38" s="47">
         <f>((4*35)/2)+18</f>
         <v>88</v>
       </c>
-      <c r="K38" s="62">
+      <c r="K38" s="47">
         <f t="shared" si="0"/>
         <v>352</v>
       </c>
-      <c r="L38" s="50">
+      <c r="L38" s="79">
         <v>43</v>
       </c>
       <c r="M38" s="17" t="s">
@@ -6755,43 +6843,43 @@
       </c>
       <c r="O38" s="18"/>
     </row>
-    <row r="39" spans="1:15" ht="17.25" customHeight="1">
+    <row r="39" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A39" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="B39" s="57" t="s">
+      <c r="B39" s="42" t="s">
         <v>218</v>
       </c>
-      <c r="C39" s="55" t="s">
+      <c r="C39" s="40" t="s">
         <v>219</v>
       </c>
-      <c r="D39" s="59" t="s">
+      <c r="D39" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F39" s="67">
+      <c r="F39" s="52">
         <v>1</v>
       </c>
       <c r="G39" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="H39" s="62">
+      <c r="H39" s="47">
         <v>227</v>
       </c>
-      <c r="I39" s="62">
-        <v>1</v>
-      </c>
-      <c r="J39" s="62">
+      <c r="I39" s="47">
+        <v>1</v>
+      </c>
+      <c r="J39" s="47">
         <f>40+14</f>
         <v>54</v>
       </c>
-      <c r="K39" s="62">
+      <c r="K39" s="47">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="L39" s="50">
+      <c r="L39" s="79">
         <v>85</v>
       </c>
       <c r="M39" s="17" t="s">
@@ -6802,43 +6890,43 @@
       </c>
       <c r="O39" s="18"/>
     </row>
-    <row r="40" spans="1:15" ht="51.75" customHeight="1">
+    <row r="40" spans="1:15" s="43" customFormat="1" ht="51.75" customHeight="1">
       <c r="A40" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="B40" s="57" t="s">
+      <c r="B40" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="C40" s="55" t="s">
+      <c r="C40" s="40" t="s">
         <v>222</v>
       </c>
-      <c r="D40" s="59" t="s">
+      <c r="D40" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E40" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F40" s="67">
+      <c r="F40" s="52">
         <v>1</v>
       </c>
       <c r="G40" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="H40" s="62">
+      <c r="H40" s="47">
         <v>158</v>
       </c>
-      <c r="I40" s="62">
-        <v>1</v>
-      </c>
-      <c r="J40" s="62">
+      <c r="I40" s="47">
+        <v>1</v>
+      </c>
+      <c r="J40" s="47">
         <f>35+9+3+5</f>
         <v>52</v>
       </c>
-      <c r="K40" s="62">
+      <c r="K40" s="47">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="L40" s="50">
+      <c r="L40" s="79">
         <v>171.5</v>
       </c>
       <c r="M40" s="17" t="s">
@@ -6849,43 +6937,43 @@
       </c>
       <c r="O40" s="18"/>
     </row>
-    <row r="41" spans="1:15" ht="17.25" customHeight="1">
+    <row r="41" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A41" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="B41" s="57" t="s">
+      <c r="B41" s="42" t="s">
         <v>225</v>
       </c>
-      <c r="C41" s="55" t="s">
+      <c r="C41" s="40" t="s">
         <v>226</v>
       </c>
-      <c r="D41" s="59" t="s">
+      <c r="D41" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E41" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F41" s="67">
+      <c r="F41" s="52">
         <v>1</v>
       </c>
       <c r="G41" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="H41" s="62">
+      <c r="H41" s="47">
         <v>325</v>
       </c>
-      <c r="I41" s="62">
-        <v>1</v>
-      </c>
-      <c r="J41" s="62">
+      <c r="I41" s="47">
+        <v>1</v>
+      </c>
+      <c r="J41" s="47">
         <f>((2*32)/2)+8</f>
         <v>40</v>
       </c>
-      <c r="K41" s="62">
+      <c r="K41" s="47">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="L41" s="50">
+      <c r="L41" s="79">
         <v>330</v>
       </c>
       <c r="M41" s="17" t="s">
@@ -6896,43 +6984,43 @@
       </c>
       <c r="O41" s="18"/>
     </row>
-    <row r="42" spans="1:15" ht="17.25" customHeight="1">
+    <row r="42" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A42" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="B42" s="57" t="s">
+      <c r="B42" s="42" t="s">
         <v>231</v>
       </c>
-      <c r="C42" s="55" t="s">
+      <c r="C42" s="40" t="s">
         <v>232</v>
       </c>
-      <c r="D42" s="59" t="s">
+      <c r="D42" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E42" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F42" s="67">
+      <c r="F42" s="52">
         <v>1</v>
       </c>
       <c r="G42" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="H42" s="62">
+      <c r="H42" s="47">
         <v>252</v>
       </c>
-      <c r="I42" s="62">
+      <c r="I42" s="47">
         <v>2</v>
       </c>
-      <c r="J42" s="62">
+      <c r="J42" s="47">
         <f>18+5</f>
         <v>23</v>
       </c>
-      <c r="K42" s="62">
+      <c r="K42" s="47">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="L42" s="50">
+      <c r="L42" s="79">
         <v>69</v>
       </c>
       <c r="M42" s="17" t="s">
@@ -6943,42 +7031,42 @@
       </c>
       <c r="O42" s="18"/>
     </row>
-    <row r="43" spans="1:15" ht="15" customHeight="1">
+    <row r="43" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A43" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="B43" s="57" t="s">
+      <c r="B43" s="42" t="s">
         <v>236</v>
       </c>
-      <c r="C43" s="55" t="s">
+      <c r="C43" s="40" t="s">
         <v>237</v>
       </c>
-      <c r="D43" s="59" t="s">
+      <c r="D43" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E43" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F43" s="67">
+      <c r="F43" s="52">
         <v>1</v>
       </c>
       <c r="G43" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="H43" s="62">
+      <c r="H43" s="47">
         <v>728</v>
       </c>
-      <c r="I43" s="62">
+      <c r="I43" s="47">
         <v>4</v>
       </c>
-      <c r="J43" s="62">
+      <c r="J43" s="47">
         <v>40</v>
       </c>
-      <c r="K43" s="62">
+      <c r="K43" s="47">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
-      <c r="L43" s="50">
+      <c r="L43" s="79">
         <v>27</v>
       </c>
       <c r="M43" s="17" t="s">
@@ -6989,42 +7077,42 @@
       </c>
       <c r="O43" s="18"/>
     </row>
-    <row r="44" spans="1:15" ht="15" customHeight="1">
+    <row r="44" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A44" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="B44" s="57" t="s">
+      <c r="B44" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="C44" s="55" t="s">
+      <c r="C44" s="40" t="s">
         <v>240</v>
       </c>
-      <c r="D44" s="59" t="s">
+      <c r="D44" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E44" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F44" s="67">
+      <c r="F44" s="52">
         <v>1</v>
       </c>
       <c r="G44" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="H44" s="62">
+      <c r="H44" s="47">
         <v>728</v>
       </c>
-      <c r="I44" s="62">
+      <c r="I44" s="47">
         <v>4</v>
       </c>
-      <c r="J44" s="62">
+      <c r="J44" s="47">
         <v>40</v>
       </c>
-      <c r="K44" s="62">
+      <c r="K44" s="47">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
-      <c r="L44" s="50">
+      <c r="L44" s="79">
         <v>15</v>
       </c>
       <c r="M44" s="17" t="s">
@@ -7035,43 +7123,43 @@
       </c>
       <c r="O44" s="18"/>
     </row>
-    <row r="45" spans="1:15" ht="17.25" customHeight="1">
+    <row r="45" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A45" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="B45" s="57" t="s">
+      <c r="B45" s="42" t="s">
         <v>242</v>
       </c>
-      <c r="C45" s="55" t="s">
+      <c r="C45" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="D45" s="59" t="s">
+      <c r="D45" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E45" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F45" s="67">
+      <c r="F45" s="52">
         <v>1</v>
       </c>
       <c r="G45" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="H45" s="62">
+      <c r="H45" s="47">
         <v>207</v>
       </c>
-      <c r="I45" s="62">
-        <v>1</v>
-      </c>
-      <c r="J45" s="62">
+      <c r="I45" s="47">
+        <v>1</v>
+      </c>
+      <c r="J45" s="47">
         <f>40+15</f>
         <v>55</v>
       </c>
-      <c r="K45" s="62">
+      <c r="K45" s="47">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="L45" s="50">
+      <c r="L45" s="79">
         <v>110</v>
       </c>
       <c r="M45" s="17" t="s">
@@ -7082,43 +7170,43 @@
       </c>
       <c r="O45" s="18"/>
     </row>
-    <row r="46" spans="1:15" ht="24" customHeight="1">
+    <row r="46" spans="1:15" s="43" customFormat="1" ht="24" customHeight="1">
       <c r="A46" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="B46" s="57" t="s">
+      <c r="B46" s="42" t="s">
         <v>246</v>
       </c>
-      <c r="C46" s="55" t="s">
+      <c r="C46" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="D46" s="59" t="s">
+      <c r="D46" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F46" s="67">
+      <c r="F46" s="52">
         <v>1</v>
       </c>
       <c r="G46" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="H46" s="62">
+      <c r="H46" s="47">
         <v>178</v>
       </c>
-      <c r="I46" s="62">
+      <c r="I46" s="47">
         <v>2</v>
       </c>
-      <c r="J46" s="62">
+      <c r="J46" s="47">
         <f>18+8+1</f>
         <v>27</v>
       </c>
-      <c r="K46" s="62">
+      <c r="K46" s="47">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="L46" s="50">
+      <c r="L46" s="79">
         <v>455</v>
       </c>
       <c r="M46" s="17" t="s">
@@ -7129,43 +7217,43 @@
       </c>
       <c r="O46" s="18"/>
     </row>
-    <row r="47" spans="1:15" ht="17.25" customHeight="1">
+    <row r="47" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A47" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="B47" s="57" t="s">
+      <c r="B47" s="42" t="s">
         <v>251</v>
       </c>
-      <c r="C47" s="55" t="s">
+      <c r="C47" s="40" t="s">
         <v>252</v>
       </c>
-      <c r="D47" s="59" t="s">
+      <c r="D47" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E47" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F47" s="67">
+      <c r="F47" s="52">
         <v>1</v>
       </c>
       <c r="G47" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="H47" s="62">
+      <c r="H47" s="47">
         <v>202</v>
       </c>
-      <c r="I47" s="62">
-        <v>1</v>
-      </c>
-      <c r="J47" s="62">
+      <c r="I47" s="47">
+        <v>1</v>
+      </c>
+      <c r="J47" s="47">
         <f>40+11</f>
         <v>51</v>
       </c>
-      <c r="K47" s="62">
+      <c r="K47" s="47">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="L47" s="50">
+      <c r="L47" s="79">
         <v>86</v>
       </c>
       <c r="M47" s="17" t="s">
@@ -7176,43 +7264,43 @@
       </c>
       <c r="O47" s="18"/>
     </row>
-    <row r="48" spans="1:15" ht="24" customHeight="1">
+    <row r="48" spans="1:15" s="43" customFormat="1" ht="24" customHeight="1">
       <c r="A48" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="B48" s="57" t="s">
+      <c r="B48" s="42" t="s">
         <v>256</v>
       </c>
-      <c r="C48" s="55" t="s">
+      <c r="C48" s="40" t="s">
         <v>257</v>
       </c>
-      <c r="D48" s="59" t="s">
+      <c r="D48" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E48" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F48" s="67">
+      <c r="F48" s="52">
         <v>1</v>
       </c>
       <c r="G48" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="H48" s="62">
+      <c r="H48" s="47">
         <v>330</v>
       </c>
-      <c r="I48" s="62">
-        <v>1</v>
-      </c>
-      <c r="J48" s="65">
+      <c r="I48" s="47">
+        <v>1</v>
+      </c>
+      <c r="J48" s="50">
         <f>((2*27)/2)+18+1.5</f>
         <v>46.5</v>
       </c>
-      <c r="K48" s="62">
+      <c r="K48" s="47">
         <f t="shared" si="0"/>
         <v>46.5</v>
       </c>
-      <c r="L48" s="50">
+      <c r="L48" s="79">
         <v>165</v>
       </c>
       <c r="M48" s="17" t="s">
@@ -7223,43 +7311,43 @@
       </c>
       <c r="O48" s="18"/>
     </row>
-    <row r="49" spans="1:15" ht="17.25" customHeight="1">
+    <row r="49" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A49" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="B49" s="57" t="s">
+      <c r="B49" s="42" t="s">
         <v>260</v>
       </c>
-      <c r="C49" s="55" t="s">
+      <c r="C49" s="40" t="s">
         <v>261</v>
       </c>
-      <c r="D49" s="59" t="s">
+      <c r="D49" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E49" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F49" s="67">
+      <c r="F49" s="52">
         <v>1</v>
       </c>
       <c r="G49" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="H49" s="62">
+      <c r="H49" s="47">
         <v>336</v>
       </c>
-      <c r="I49" s="62">
+      <c r="I49" s="47">
         <v>2</v>
       </c>
-      <c r="J49" s="62">
+      <c r="J49" s="47">
         <f>((4*40)/2)+20</f>
         <v>100</v>
       </c>
-      <c r="K49" s="62">
+      <c r="K49" s="47">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="L49" s="50">
+      <c r="L49" s="79">
         <v>13.5</v>
       </c>
       <c r="M49" s="17" t="s">
@@ -7270,42 +7358,42 @@
       </c>
       <c r="O49" s="18"/>
     </row>
-    <row r="50" spans="1:15" ht="15" customHeight="1">
+    <row r="50" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A50" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="B50" s="57" t="s">
+      <c r="B50" s="42" t="s">
         <v>263</v>
       </c>
-      <c r="C50" s="55" t="s">
+      <c r="C50" s="40" t="s">
         <v>264</v>
       </c>
-      <c r="D50" s="59" t="s">
+      <c r="D50" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E50" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F50" s="67">
+      <c r="F50" s="52">
         <v>1</v>
       </c>
       <c r="G50" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="H50" s="62">
+      <c r="H50" s="47">
         <v>728</v>
       </c>
-      <c r="I50" s="62">
+      <c r="I50" s="47">
         <v>4</v>
       </c>
-      <c r="J50" s="62">
+      <c r="J50" s="47">
         <v>40</v>
       </c>
-      <c r="K50" s="62">
+      <c r="K50" s="47">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
-      <c r="L50" s="50">
+      <c r="L50" s="79">
         <v>27</v>
       </c>
       <c r="M50" s="17" t="s">
@@ -7316,42 +7404,42 @@
       </c>
       <c r="O50" s="18"/>
     </row>
-    <row r="51" spans="1:15" ht="15" customHeight="1">
+    <row r="51" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A51" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="B51" s="57" t="s">
+      <c r="B51" s="42" t="s">
         <v>266</v>
       </c>
-      <c r="C51" s="55" t="s">
+      <c r="C51" s="40" t="s">
         <v>267</v>
       </c>
-      <c r="D51" s="59" t="s">
+      <c r="D51" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E51" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F51" s="67">
+      <c r="F51" s="52">
         <v>1</v>
       </c>
       <c r="G51" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="H51" s="62">
+      <c r="H51" s="47">
         <v>728</v>
       </c>
-      <c r="I51" s="62">
+      <c r="I51" s="47">
         <v>4</v>
       </c>
-      <c r="J51" s="62">
+      <c r="J51" s="47">
         <v>40</v>
       </c>
-      <c r="K51" s="62">
+      <c r="K51" s="47">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
-      <c r="L51" s="50">
+      <c r="L51" s="79">
         <v>57.5</v>
       </c>
       <c r="M51" s="17" t="s">
@@ -7362,42 +7450,42 @@
       </c>
       <c r="O51" s="18"/>
     </row>
-    <row r="52" spans="1:15" ht="15" customHeight="1">
+    <row r="52" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A52" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B52" s="57" t="s">
+      <c r="B52" s="42" t="s">
         <v>269</v>
       </c>
-      <c r="C52" s="55" t="s">
+      <c r="C52" s="40" t="s">
         <v>270</v>
       </c>
-      <c r="D52" s="59" t="s">
+      <c r="D52" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E52" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F52" s="67">
+      <c r="F52" s="52">
         <v>1</v>
       </c>
       <c r="G52" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="H52" s="62">
+      <c r="H52" s="47">
         <v>1428</v>
       </c>
-      <c r="I52" s="62">
+      <c r="I52" s="47">
         <v>4</v>
       </c>
-      <c r="J52" s="62">
+      <c r="J52" s="47">
         <v>40</v>
       </c>
-      <c r="K52" s="62">
+      <c r="K52" s="47">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
-      <c r="L52" s="50">
+      <c r="L52" s="79">
         <v>11.5</v>
       </c>
       <c r="M52" s="17" t="s">
@@ -7408,43 +7496,43 @@
       </c>
       <c r="O52" s="18"/>
     </row>
-    <row r="53" spans="1:15" ht="24" customHeight="1">
+    <row r="53" spans="1:15" s="43" customFormat="1" ht="24" customHeight="1">
       <c r="A53" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="B53" s="57" t="s">
+      <c r="B53" s="42" t="s">
         <v>272</v>
       </c>
-      <c r="C53" s="55" t="s">
+      <c r="C53" s="40" t="s">
         <v>273</v>
       </c>
-      <c r="D53" s="59" t="s">
+      <c r="D53" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E53" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F53" s="67">
+      <c r="F53" s="52">
         <v>1</v>
       </c>
       <c r="G53" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="H53" s="62">
+      <c r="H53" s="47">
         <v>378</v>
       </c>
-      <c r="I53" s="62">
+      <c r="I53" s="47">
         <v>3</v>
       </c>
-      <c r="J53" s="65">
+      <c r="J53" s="50">
         <f>18+0.333333333333333</f>
         <v>18.333333333333332</v>
       </c>
-      <c r="K53" s="62">
+      <c r="K53" s="47">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="L53" s="50">
+      <c r="L53" s="79">
         <v>12</v>
       </c>
       <c r="M53" s="17" t="s">
@@ -7455,43 +7543,43 @@
       </c>
       <c r="O53" s="18"/>
     </row>
-    <row r="54" spans="1:15" ht="17.25" customHeight="1">
+    <row r="54" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A54" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="B54" s="57" t="s">
+      <c r="B54" s="42" t="s">
         <v>276</v>
       </c>
-      <c r="C54" s="55" t="s">
+      <c r="C54" s="40" t="s">
         <v>277</v>
       </c>
-      <c r="D54" s="59" t="s">
+      <c r="D54" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E54" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F54" s="67">
+      <c r="F54" s="52">
         <v>1</v>
       </c>
       <c r="G54" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="H54" s="62">
+      <c r="H54" s="47">
         <v>286</v>
       </c>
-      <c r="I54" s="62">
+      <c r="I54" s="47">
         <v>2</v>
       </c>
-      <c r="J54" s="62">
+      <c r="J54" s="47">
         <f>32+6</f>
         <v>38</v>
       </c>
-      <c r="K54" s="62">
+      <c r="K54" s="47">
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="L54" s="50">
+      <c r="L54" s="79">
         <v>152</v>
       </c>
       <c r="M54" s="17" t="s">
@@ -7502,43 +7590,43 @@
       </c>
       <c r="O54" s="18"/>
     </row>
-    <row r="55" spans="1:15" ht="17.25" customHeight="1">
+    <row r="55" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A55" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="B55" s="57" t="s">
+      <c r="B55" s="42" t="s">
         <v>280</v>
       </c>
-      <c r="C55" s="55" t="s">
+      <c r="C55" s="40" t="s">
         <v>281</v>
       </c>
-      <c r="D55" s="59" t="s">
+      <c r="D55" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E55" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F55" s="67">
+      <c r="F55" s="52">
         <v>1</v>
       </c>
       <c r="G55" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="H55" s="62">
+      <c r="H55" s="47">
         <v>902</v>
       </c>
-      <c r="I55" s="62">
+      <c r="I55" s="47">
         <v>2</v>
       </c>
-      <c r="J55" s="62">
+      <c r="J55" s="47">
         <f>((4*40)/2)+20</f>
         <v>100</v>
       </c>
-      <c r="K55" s="62">
+      <c r="K55" s="47">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="L55" s="50">
+      <c r="L55" s="79">
         <v>29.5</v>
       </c>
       <c r="M55" s="17" t="s">
@@ -7549,43 +7637,43 @@
       </c>
       <c r="O55" s="18"/>
     </row>
-    <row r="56" spans="1:15" ht="25.5" customHeight="1">
+    <row r="56" spans="1:15" s="43" customFormat="1" ht="25.5" customHeight="1">
       <c r="A56" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="B56" s="57" t="s">
+      <c r="B56" s="42" t="s">
         <v>283</v>
       </c>
-      <c r="C56" s="55" t="s">
+      <c r="C56" s="40" t="s">
         <v>284</v>
       </c>
-      <c r="D56" s="59" t="s">
+      <c r="D56" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E56" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F56" s="67">
+      <c r="F56" s="52">
         <v>1</v>
       </c>
       <c r="G56" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="H56" s="62">
+      <c r="H56" s="47">
         <v>85</v>
       </c>
-      <c r="I56" s="62">
-        <v>1</v>
-      </c>
-      <c r="J56" s="62">
+      <c r="I56" s="47">
+        <v>1</v>
+      </c>
+      <c r="J56" s="47">
         <f>20+7+1</f>
         <v>28</v>
       </c>
-      <c r="K56" s="62">
+      <c r="K56" s="47">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="L56" s="50">
+      <c r="L56" s="79">
         <v>31.74</v>
       </c>
       <c r="M56" s="17" t="s">
@@ -7596,43 +7684,43 @@
       </c>
       <c r="O56" s="18"/>
     </row>
-    <row r="57" spans="1:15" ht="17.25" customHeight="1">
+    <row r="57" spans="1:15" s="43" customFormat="1" ht="17.25" customHeight="1">
       <c r="A57" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="B57" s="57" t="s">
+      <c r="B57" s="42" t="s">
         <v>288</v>
       </c>
-      <c r="C57" s="55" t="s">
+      <c r="C57" s="40" t="s">
         <v>289</v>
       </c>
-      <c r="D57" s="59" t="s">
+      <c r="D57" s="44" t="s">
         <v>1089</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F57" s="67">
+      <c r="F57" s="52">
         <v>1</v>
       </c>
       <c r="G57" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="H57" s="62">
+      <c r="H57" s="47">
         <v>600</v>
       </c>
-      <c r="I57" s="62">
+      <c r="I57" s="47">
         <v>4</v>
       </c>
-      <c r="J57" s="62">
+      <c r="J57" s="47">
         <f>((4*35)/2)+18</f>
         <v>88</v>
       </c>
-      <c r="K57" s="62">
+      <c r="K57" s="47">
         <f t="shared" si="0"/>
         <v>352</v>
       </c>
-      <c r="L57" s="50">
+      <c r="L57" s="79">
         <v>19.5</v>
       </c>
       <c r="M57" s="17" t="s">
@@ -7643,33 +7731,33 @@
       </c>
       <c r="O57" s="18"/>
     </row>
-    <row r="58" spans="1:15" ht="24" customHeight="1">
+    <row r="58" spans="1:15" s="43" customFormat="1" ht="24" customHeight="1">
       <c r="A58" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B58" s="57" t="s">
+      <c r="B58" s="42" t="s">
         <v>292</v>
       </c>
-      <c r="C58" s="55" t="s">
+      <c r="C58" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="D58" s="59"/>
+      <c r="D58" s="44"/>
       <c r="E58" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F58" s="67">
+      <c r="F58" s="52">
         <v>1</v>
       </c>
       <c r="G58" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="H58" s="63"/>
-      <c r="I58" s="63"/>
-      <c r="J58" s="63"/>
-      <c r="K58" s="63">
+      <c r="H58" s="48"/>
+      <c r="I58" s="48"/>
+      <c r="J58" s="48"/>
+      <c r="K58" s="48">
         <v>30</v>
       </c>
-      <c r="L58" s="50">
+      <c r="L58" s="79">
         <v>115</v>
       </c>
       <c r="M58" s="18"/>
@@ -7678,33 +7766,33 @@
         <v>294</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="15" customHeight="1">
+    <row r="59" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A59" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B59" s="57" t="s">
+      <c r="B59" s="42" t="s">
         <v>295</v>
       </c>
-      <c r="C59" s="55" t="s">
+      <c r="C59" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="D59" s="59"/>
+      <c r="D59" s="44"/>
       <c r="E59" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F59" s="67">
+      <c r="F59" s="52">
         <v>1</v>
       </c>
       <c r="G59" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="H59" s="63"/>
-      <c r="I59" s="63"/>
-      <c r="J59" s="63"/>
-      <c r="K59" s="63">
+      <c r="H59" s="48"/>
+      <c r="I59" s="48"/>
+      <c r="J59" s="48"/>
+      <c r="K59" s="48">
         <v>5</v>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="79">
         <v>135</v>
       </c>
       <c r="M59" s="18"/>
@@ -7713,33 +7801,33 @@
         <v>297</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="15" customHeight="1">
+    <row r="60" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A60" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B60" s="57" t="s">
+      <c r="B60" s="42" t="s">
         <v>298</v>
       </c>
-      <c r="C60" s="55" t="s">
+      <c r="C60" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="D60" s="59"/>
+      <c r="D60" s="44"/>
       <c r="E60" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F60" s="67">
+      <c r="F60" s="52">
         <v>1</v>
       </c>
       <c r="G60" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="H60" s="63"/>
-      <c r="I60" s="63"/>
-      <c r="J60" s="63"/>
-      <c r="K60" s="63">
+      <c r="H60" s="48"/>
+      <c r="I60" s="48"/>
+      <c r="J60" s="48"/>
+      <c r="K60" s="48">
         <v>3</v>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="79">
         <v>100</v>
       </c>
       <c r="M60" s="18"/>
@@ -7748,33 +7836,33 @@
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="15" customHeight="1">
+    <row r="61" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A61" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B61" s="57" t="s">
+      <c r="B61" s="42" t="s">
         <v>301</v>
       </c>
-      <c r="C61" s="55" t="s">
+      <c r="C61" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="D61" s="59"/>
+      <c r="D61" s="44"/>
       <c r="E61" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F61" s="67">
+      <c r="F61" s="52">
         <v>1</v>
       </c>
       <c r="G61" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="H61" s="63"/>
-      <c r="I61" s="63"/>
-      <c r="J61" s="63"/>
-      <c r="K61" s="63">
+      <c r="H61" s="48"/>
+      <c r="I61" s="48"/>
+      <c r="J61" s="48"/>
+      <c r="K61" s="48">
         <v>5</v>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="79">
         <v>100</v>
       </c>
       <c r="M61" s="18"/>
@@ -7783,33 +7871,33 @@
         <v>302</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="15" customHeight="1">
+    <row r="62" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A62" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B62" s="57" t="s">
+      <c r="B62" s="42" t="s">
         <v>303</v>
       </c>
-      <c r="C62" s="55" t="s">
+      <c r="C62" s="40" t="s">
         <v>228</v>
       </c>
-      <c r="D62" s="59"/>
+      <c r="D62" s="44"/>
       <c r="E62" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F62" s="67">
+      <c r="F62" s="52">
         <v>1</v>
       </c>
       <c r="G62" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="H62" s="63"/>
-      <c r="I62" s="63"/>
-      <c r="J62" s="63"/>
-      <c r="K62" s="63">
+      <c r="H62" s="48"/>
+      <c r="I62" s="48"/>
+      <c r="J62" s="48"/>
+      <c r="K62" s="48">
         <v>3</v>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="79">
         <v>200</v>
       </c>
       <c r="M62" s="18"/>
@@ -7818,33 +7906,33 @@
         <v>304</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="15" customHeight="1">
+    <row r="63" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A63" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B63" s="57" t="s">
+      <c r="B63" s="42" t="s">
         <v>305</v>
       </c>
-      <c r="C63" s="55" t="s">
+      <c r="C63" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="D63" s="59"/>
+      <c r="D63" s="44"/>
       <c r="E63" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F63" s="67">
+      <c r="F63" s="52">
         <v>1</v>
       </c>
       <c r="G63" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="H63" s="63"/>
-      <c r="I63" s="63"/>
-      <c r="J63" s="63"/>
-      <c r="K63" s="63">
+      <c r="H63" s="48"/>
+      <c r="I63" s="48"/>
+      <c r="J63" s="48"/>
+      <c r="K63" s="48">
         <v>3</v>
       </c>
-      <c r="L63" s="50">
+      <c r="L63" s="79">
         <v>90</v>
       </c>
       <c r="M63" s="18"/>
@@ -7853,33 +7941,33 @@
         <v>306</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="15" customHeight="1">
+    <row r="64" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A64" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B64" s="57" t="s">
+      <c r="B64" s="42" t="s">
         <v>307</v>
       </c>
-      <c r="C64" s="55" t="s">
+      <c r="C64" s="40" t="s">
         <v>308</v>
       </c>
-      <c r="D64" s="59"/>
+      <c r="D64" s="44"/>
       <c r="E64" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F64" s="67">
+      <c r="F64" s="52">
         <v>1</v>
       </c>
       <c r="G64" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="H64" s="63"/>
-      <c r="I64" s="63"/>
-      <c r="J64" s="63"/>
-      <c r="K64" s="63">
+      <c r="H64" s="48"/>
+      <c r="I64" s="48"/>
+      <c r="J64" s="48"/>
+      <c r="K64" s="48">
         <v>4</v>
       </c>
-      <c r="L64" s="50">
+      <c r="L64" s="79">
         <v>292</v>
       </c>
       <c r="M64" s="18"/>
@@ -7888,33 +7976,33 @@
         <v>310</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="15" customHeight="1">
+    <row r="65" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A65" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B65" s="57" t="s">
+      <c r="B65" s="42" t="s">
         <v>311</v>
       </c>
-      <c r="C65" s="55" t="s">
+      <c r="C65" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="D65" s="59"/>
+      <c r="D65" s="44"/>
       <c r="E65" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F65" s="67">
+      <c r="F65" s="52">
         <v>1</v>
       </c>
       <c r="G65" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="H65" s="63"/>
-      <c r="I65" s="63"/>
-      <c r="J65" s="63"/>
-      <c r="K65" s="63">
-        <v>1</v>
-      </c>
-      <c r="L65" s="50">
+      <c r="H65" s="48"/>
+      <c r="I65" s="48"/>
+      <c r="J65" s="48"/>
+      <c r="K65" s="48">
+        <v>1</v>
+      </c>
+      <c r="L65" s="79">
         <v>63</v>
       </c>
       <c r="M65" s="18"/>
@@ -7923,33 +8011,33 @@
         <v>313</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="15" customHeight="1">
+    <row r="66" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A66" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B66" s="57" t="s">
+      <c r="B66" s="42" t="s">
         <v>314</v>
       </c>
-      <c r="C66" s="55" t="s">
+      <c r="C66" s="40" t="s">
         <v>286</v>
       </c>
-      <c r="D66" s="59"/>
+      <c r="D66" s="44"/>
       <c r="E66" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F66" s="67">
+      <c r="F66" s="52">
         <v>1</v>
       </c>
       <c r="G66" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="H66" s="63"/>
-      <c r="I66" s="63"/>
-      <c r="J66" s="63"/>
-      <c r="K66" s="63">
-        <v>1</v>
-      </c>
-      <c r="L66" s="50">
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="J66" s="48"/>
+      <c r="K66" s="48">
+        <v>1</v>
+      </c>
+      <c r="L66" s="79">
         <v>8</v>
       </c>
       <c r="M66" s="18"/>
@@ -7958,33 +8046,33 @@
         <v>315</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="15" customHeight="1">
+    <row r="67" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A67" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B67" s="57" t="s">
+      <c r="B67" s="42" t="s">
         <v>316</v>
       </c>
-      <c r="C67" s="55" t="s">
+      <c r="C67" s="40" t="s">
         <v>317</v>
       </c>
-      <c r="D67" s="59"/>
+      <c r="D67" s="44"/>
       <c r="E67" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="67">
+      <c r="F67" s="52">
         <v>1</v>
       </c>
       <c r="G67" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="H67" s="63"/>
-      <c r="I67" s="63"/>
-      <c r="J67" s="63"/>
-      <c r="K67" s="63">
+      <c r="H67" s="48"/>
+      <c r="I67" s="48"/>
+      <c r="J67" s="48"/>
+      <c r="K67" s="48">
         <v>6</v>
       </c>
-      <c r="L67" s="50">
+      <c r="L67" s="79">
         <v>283</v>
       </c>
       <c r="M67" s="18"/>
@@ -7993,33 +8081,33 @@
         <v>319</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="15" customHeight="1">
+    <row r="68" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A68" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B68" s="57" t="s">
+      <c r="B68" s="42" t="s">
         <v>320</v>
       </c>
-      <c r="C68" s="55" t="s">
+      <c r="C68" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="D68" s="59"/>
+      <c r="D68" s="44"/>
       <c r="E68" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F68" s="67">
+      <c r="F68" s="52">
         <v>1</v>
       </c>
       <c r="G68" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="H68" s="63"/>
-      <c r="I68" s="63"/>
-      <c r="J68" s="63"/>
-      <c r="K68" s="63">
+      <c r="H68" s="48"/>
+      <c r="I68" s="48"/>
+      <c r="J68" s="48"/>
+      <c r="K68" s="48">
         <v>8</v>
       </c>
-      <c r="L68" s="50">
+      <c r="L68" s="79">
         <v>297.2</v>
       </c>
       <c r="M68" s="18"/>
@@ -8028,33 +8116,33 @@
         <v>322</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="15" customHeight="1">
+    <row r="69" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A69" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B69" s="57" t="s">
+      <c r="B69" s="42" t="s">
         <v>323</v>
       </c>
-      <c r="C69" s="55" t="s">
+      <c r="C69" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="D69" s="59"/>
+      <c r="D69" s="44"/>
       <c r="E69" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F69" s="67">
+      <c r="F69" s="52">
         <v>1</v>
       </c>
       <c r="G69" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="H69" s="63"/>
-      <c r="I69" s="63"/>
-      <c r="J69" s="63"/>
-      <c r="K69" s="63">
-        <v>1</v>
-      </c>
-      <c r="L69" s="50">
+      <c r="H69" s="48"/>
+      <c r="I69" s="48"/>
+      <c r="J69" s="48"/>
+      <c r="K69" s="48">
+        <v>1</v>
+      </c>
+      <c r="L69" s="79">
         <v>102</v>
       </c>
       <c r="M69" s="18"/>
@@ -8063,33 +8151,33 @@
         <v>324</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="15" customHeight="1">
+    <row r="70" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A70" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B70" s="57" t="s">
+      <c r="B70" s="42" t="s">
         <v>325</v>
       </c>
-      <c r="C70" s="55" t="s">
+      <c r="C70" s="40" t="s">
         <v>234</v>
       </c>
-      <c r="D70" s="59"/>
+      <c r="D70" s="44"/>
       <c r="E70" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F70" s="67">
+      <c r="F70" s="52">
         <v>1</v>
       </c>
       <c r="G70" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="H70" s="63"/>
-      <c r="I70" s="63"/>
-      <c r="J70" s="63"/>
-      <c r="K70" s="63">
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="48"/>
+      <c r="K70" s="48">
         <v>5</v>
       </c>
-      <c r="L70" s="50">
+      <c r="L70" s="79">
         <v>75.8</v>
       </c>
       <c r="M70" s="18"/>
@@ -8098,33 +8186,33 @@
         <v>327</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="15" customHeight="1">
+    <row r="71" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A71" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B71" s="57" t="s">
+      <c r="B71" s="42" t="s">
         <v>328</v>
       </c>
-      <c r="C71" s="55" t="s">
+      <c r="C71" s="40" t="s">
         <v>254</v>
       </c>
-      <c r="D71" s="59"/>
+      <c r="D71" s="44"/>
       <c r="E71" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F71" s="67">
+      <c r="F71" s="52">
         <v>1</v>
       </c>
       <c r="G71" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="H71" s="63"/>
-      <c r="I71" s="63"/>
-      <c r="J71" s="63"/>
-      <c r="K71" s="63">
+      <c r="H71" s="48"/>
+      <c r="I71" s="48"/>
+      <c r="J71" s="48"/>
+      <c r="K71" s="48">
         <v>5</v>
       </c>
-      <c r="L71" s="50">
+      <c r="L71" s="79">
         <v>154.80000000000001</v>
       </c>
       <c r="M71" s="18"/>
@@ -8133,33 +8221,33 @@
         <v>329</v>
       </c>
     </row>
-    <row r="72" spans="1:15" ht="15" customHeight="1">
+    <row r="72" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A72" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B72" s="57" t="s">
+      <c r="B72" s="42" t="s">
         <v>330</v>
       </c>
-      <c r="C72" s="55" t="s">
+      <c r="C72" s="40" t="s">
         <v>331</v>
       </c>
-      <c r="D72" s="59"/>
+      <c r="D72" s="44"/>
       <c r="E72" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F72" s="67">
+      <c r="F72" s="52">
         <v>1</v>
       </c>
       <c r="G72" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="H72" s="63"/>
-      <c r="I72" s="63"/>
-      <c r="J72" s="63"/>
-      <c r="K72" s="63">
-        <v>1</v>
-      </c>
-      <c r="L72" s="50">
+      <c r="H72" s="48"/>
+      <c r="I72" s="48"/>
+      <c r="J72" s="48"/>
+      <c r="K72" s="48">
+        <v>1</v>
+      </c>
+      <c r="L72" s="79">
         <v>10</v>
       </c>
       <c r="M72" s="18"/>
@@ -8168,33 +8256,33 @@
         <v>332</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="15" customHeight="1">
+    <row r="73" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A73" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B73" s="57" t="s">
+      <c r="B73" s="42" t="s">
         <v>333</v>
       </c>
-      <c r="C73" s="55" t="s">
+      <c r="C73" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="D73" s="59"/>
+      <c r="D73" s="44"/>
       <c r="E73" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F73" s="67">
+      <c r="F73" s="52">
         <v>1</v>
       </c>
       <c r="G73" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="H73" s="63"/>
-      <c r="I73" s="63"/>
-      <c r="J73" s="63"/>
-      <c r="K73" s="63">
+      <c r="H73" s="48"/>
+      <c r="I73" s="48"/>
+      <c r="J73" s="48"/>
+      <c r="K73" s="48">
         <v>2</v>
       </c>
-      <c r="L73" s="50">
+      <c r="L73" s="79">
         <v>155</v>
       </c>
       <c r="M73" s="18"/>
@@ -8203,33 +8291,33 @@
         <v>335</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="15" customHeight="1">
+    <row r="74" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A74" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B74" s="57" t="s">
+      <c r="B74" s="42" t="s">
         <v>336</v>
       </c>
-      <c r="C74" s="55" t="s">
+      <c r="C74" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="D74" s="59"/>
+      <c r="D74" s="44"/>
       <c r="E74" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F74" s="67">
+      <c r="F74" s="52">
         <v>1</v>
       </c>
       <c r="G74" s="14" t="s">
         <v>337</v>
       </c>
-      <c r="H74" s="63"/>
-      <c r="I74" s="63"/>
-      <c r="J74" s="69"/>
-      <c r="K74" s="69">
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
+      <c r="J74" s="54"/>
+      <c r="K74" s="54">
         <v>0.5</v>
       </c>
-      <c r="L74" s="50">
+      <c r="L74" s="79">
         <v>50</v>
       </c>
       <c r="M74" s="18"/>
@@ -8238,33 +8326,33 @@
         <v>338</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="15" customHeight="1">
+    <row r="75" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A75" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B75" s="57" t="s">
+      <c r="B75" s="42" t="s">
         <v>339</v>
       </c>
-      <c r="C75" s="55" t="s">
+      <c r="C75" s="40" t="s">
         <v>340</v>
       </c>
-      <c r="D75" s="59"/>
+      <c r="D75" s="44"/>
       <c r="E75" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F75" s="67">
+      <c r="F75" s="52">
         <v>1</v>
       </c>
       <c r="G75" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="H75" s="63"/>
-      <c r="I75" s="63"/>
-      <c r="J75" s="69"/>
-      <c r="K75" s="69">
+      <c r="H75" s="48"/>
+      <c r="I75" s="48"/>
+      <c r="J75" s="54"/>
+      <c r="K75" s="54">
         <v>2.5</v>
       </c>
-      <c r="L75" s="50">
+      <c r="L75" s="79">
         <v>193</v>
       </c>
       <c r="M75" s="18"/>
@@ -8273,33 +8361,33 @@
         <v>342</v>
       </c>
     </row>
-    <row r="76" spans="1:15" ht="15" customHeight="1">
+    <row r="76" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A76" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B76" s="57" t="s">
+      <c r="B76" s="42" t="s">
         <v>343</v>
       </c>
-      <c r="C76" s="55" t="s">
+      <c r="C76" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="D76" s="59"/>
+      <c r="D76" s="44"/>
       <c r="E76" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F76" s="67">
+      <c r="F76" s="52">
         <v>1</v>
       </c>
       <c r="G76" s="14" t="s">
         <v>344</v>
       </c>
-      <c r="H76" s="63"/>
-      <c r="I76" s="63"/>
-      <c r="J76" s="63"/>
-      <c r="K76" s="63">
-        <v>1</v>
-      </c>
-      <c r="L76" s="50">
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
+      <c r="J76" s="48"/>
+      <c r="K76" s="48">
+        <v>1</v>
+      </c>
+      <c r="L76" s="79">
         <v>19</v>
       </c>
       <c r="M76" s="18"/>
@@ -8308,33 +8396,33 @@
         <v>345</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="15" customHeight="1">
+    <row r="77" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A77" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B77" s="57" t="s">
+      <c r="B77" s="42" t="s">
         <v>346</v>
       </c>
-      <c r="C77" s="55" t="s">
+      <c r="C77" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="D77" s="59"/>
+      <c r="D77" s="44"/>
       <c r="E77" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F77" s="67">
+      <c r="F77" s="52">
         <v>1</v>
       </c>
       <c r="G77" s="14" t="s">
         <v>347</v>
       </c>
-      <c r="H77" s="63"/>
-      <c r="I77" s="63"/>
-      <c r="J77" s="69"/>
-      <c r="K77" s="69">
+      <c r="H77" s="48"/>
+      <c r="I77" s="48"/>
+      <c r="J77" s="54"/>
+      <c r="K77" s="54">
         <v>2.5</v>
       </c>
-      <c r="L77" s="50">
+      <c r="L77" s="79">
         <v>145</v>
       </c>
       <c r="M77" s="18"/>
@@ -8343,33 +8431,33 @@
         <v>348</v>
       </c>
     </row>
-    <row r="78" spans="1:15" ht="15" customHeight="1">
+    <row r="78" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A78" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B78" s="57" t="s">
+      <c r="B78" s="42" t="s">
         <v>349</v>
       </c>
-      <c r="C78" s="55" t="s">
+      <c r="C78" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="D78" s="59"/>
+      <c r="D78" s="44"/>
       <c r="E78" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F78" s="67">
+      <c r="F78" s="52">
         <v>1</v>
       </c>
       <c r="G78" s="14" t="s">
         <v>347</v>
       </c>
-      <c r="H78" s="63"/>
-      <c r="I78" s="63"/>
-      <c r="J78" s="69"/>
-      <c r="K78" s="69">
+      <c r="H78" s="48"/>
+      <c r="I78" s="48"/>
+      <c r="J78" s="54"/>
+      <c r="K78" s="54">
         <v>2.5</v>
       </c>
-      <c r="L78" s="50">
+      <c r="L78" s="79">
         <v>78.599999999999994</v>
       </c>
       <c r="M78" s="18"/>
@@ -8378,33 +8466,33 @@
         <v>350</v>
       </c>
     </row>
-    <row r="79" spans="1:15" ht="15" customHeight="1">
+    <row r="79" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A79" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B79" s="57" t="s">
+      <c r="B79" s="42" t="s">
         <v>351</v>
       </c>
-      <c r="C79" s="55" t="s">
+      <c r="C79" s="40" t="s">
         <v>352</v>
       </c>
-      <c r="D79" s="59"/>
+      <c r="D79" s="44"/>
       <c r="E79" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F79" s="67">
+      <c r="F79" s="52">
         <v>1</v>
       </c>
       <c r="G79" s="14" t="s">
         <v>347</v>
       </c>
-      <c r="H79" s="63"/>
-      <c r="I79" s="63"/>
-      <c r="J79" s="69"/>
-      <c r="K79" s="69">
+      <c r="H79" s="48"/>
+      <c r="I79" s="48"/>
+      <c r="J79" s="54"/>
+      <c r="K79" s="54">
         <v>2.5</v>
       </c>
-      <c r="L79" s="50">
+      <c r="L79" s="79">
         <v>47.6</v>
       </c>
       <c r="M79" s="18"/>
@@ -8413,33 +8501,33 @@
         <v>353</v>
       </c>
     </row>
-    <row r="80" spans="1:15" ht="15" customHeight="1">
+    <row r="80" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A80" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B80" s="57" t="s">
+      <c r="B80" s="42" t="s">
         <v>354</v>
       </c>
-      <c r="C80" s="55" t="s">
+      <c r="C80" s="40" t="s">
         <v>355</v>
       </c>
-      <c r="D80" s="59"/>
+      <c r="D80" s="44"/>
       <c r="E80" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F80" s="67">
+      <c r="F80" s="52">
         <v>1</v>
       </c>
       <c r="G80" s="14" t="s">
         <v>347</v>
       </c>
-      <c r="H80" s="63"/>
-      <c r="I80" s="63"/>
-      <c r="J80" s="69"/>
-      <c r="K80" s="69">
+      <c r="H80" s="48"/>
+      <c r="I80" s="48"/>
+      <c r="J80" s="54"/>
+      <c r="K80" s="54">
         <v>2.5</v>
       </c>
-      <c r="L80" s="50">
+      <c r="L80" s="79">
         <v>47.6</v>
       </c>
       <c r="M80" s="18"/>
@@ -8448,33 +8536,33 @@
         <v>356</v>
       </c>
     </row>
-    <row r="81" spans="1:15" ht="24" customHeight="1">
+    <row r="81" spans="1:15" s="43" customFormat="1" ht="24" customHeight="1">
       <c r="A81" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B81" s="57" t="s">
+      <c r="B81" s="42" t="s">
         <v>359</v>
       </c>
-      <c r="C81" s="55" t="s">
+      <c r="C81" s="40" t="s">
         <v>360</v>
       </c>
-      <c r="D81" s="59"/>
+      <c r="D81" s="44"/>
       <c r="E81" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F81" s="67">
+      <c r="F81" s="52">
         <v>1</v>
       </c>
       <c r="G81" s="14" t="s">
         <v>361</v>
       </c>
-      <c r="H81" s="63"/>
-      <c r="I81" s="63"/>
-      <c r="J81" s="63"/>
-      <c r="K81" s="63">
+      <c r="H81" s="48"/>
+      <c r="I81" s="48"/>
+      <c r="J81" s="48"/>
+      <c r="K81" s="48">
         <v>50</v>
       </c>
-      <c r="L81" s="50">
+      <c r="L81" s="79">
         <v>115</v>
       </c>
       <c r="M81" s="18"/>
@@ -8485,33 +8573,33 @@
         <v>294</v>
       </c>
     </row>
-    <row r="82" spans="1:15" ht="24" customHeight="1">
+    <row r="82" spans="1:15" s="43" customFormat="1" ht="24" customHeight="1">
       <c r="A82" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B82" s="57" t="s">
+      <c r="B82" s="42" t="s">
         <v>363</v>
       </c>
-      <c r="C82" s="55" t="s">
+      <c r="C82" s="40" t="s">
         <v>364</v>
       </c>
-      <c r="D82" s="59"/>
+      <c r="D82" s="44"/>
       <c r="E82" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F82" s="67">
+      <c r="F82" s="52">
         <v>1</v>
       </c>
       <c r="G82" s="14" t="s">
         <v>361</v>
       </c>
-      <c r="H82" s="63"/>
-      <c r="I82" s="63"/>
-      <c r="J82" s="63"/>
-      <c r="K82" s="63">
+      <c r="H82" s="48"/>
+      <c r="I82" s="48"/>
+      <c r="J82" s="48"/>
+      <c r="K82" s="48">
         <v>50</v>
       </c>
-      <c r="L82" s="50">
+      <c r="L82" s="79">
         <v>115</v>
       </c>
       <c r="M82" s="18"/>
@@ -8522,33 +8610,33 @@
         <v>294</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="15" customHeight="1">
+    <row r="83" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A83" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B83" s="57" t="s">
+      <c r="B83" s="42" t="s">
         <v>365</v>
       </c>
-      <c r="C83" s="55" t="s">
+      <c r="C83" s="40" t="s">
         <v>366</v>
       </c>
-      <c r="D83" s="59"/>
+      <c r="D83" s="44"/>
       <c r="E83" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F83" s="67">
+      <c r="F83" s="52">
         <v>1</v>
       </c>
       <c r="G83" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="H83" s="63"/>
-      <c r="I83" s="63"/>
-      <c r="J83" s="63"/>
-      <c r="K83" s="63">
+      <c r="H83" s="48"/>
+      <c r="I83" s="48"/>
+      <c r="J83" s="48"/>
+      <c r="K83" s="48">
         <v>4</v>
       </c>
-      <c r="L83" s="50">
+      <c r="L83" s="79">
         <v>190</v>
       </c>
       <c r="M83" s="18"/>
@@ -8559,33 +8647,33 @@
         <v>304</v>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="15" customHeight="1">
+    <row r="84" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A84" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B84" s="57" t="s">
+      <c r="B84" s="42" t="s">
         <v>368</v>
       </c>
-      <c r="C84" s="55" t="s">
+      <c r="C84" s="40" t="s">
         <v>369</v>
       </c>
-      <c r="D84" s="59"/>
+      <c r="D84" s="44"/>
       <c r="E84" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F84" s="67">
+      <c r="F84" s="52">
         <v>1</v>
       </c>
       <c r="G84" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="H84" s="63"/>
-      <c r="I84" s="63"/>
-      <c r="J84" s="63"/>
-      <c r="K84" s="63">
+      <c r="H84" s="48"/>
+      <c r="I84" s="48"/>
+      <c r="J84" s="48"/>
+      <c r="K84" s="48">
         <v>4</v>
       </c>
-      <c r="L84" s="50">
+      <c r="L84" s="79">
         <v>260</v>
       </c>
       <c r="M84" s="18"/>
@@ -8596,33 +8684,33 @@
         <v>335</v>
       </c>
     </row>
-    <row r="85" spans="1:15" ht="15" customHeight="1">
+    <row r="85" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A85" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B85" s="57" t="s">
+      <c r="B85" s="42" t="s">
         <v>371</v>
       </c>
-      <c r="C85" s="55" t="s">
+      <c r="C85" s="40" t="s">
         <v>372</v>
       </c>
-      <c r="D85" s="59"/>
+      <c r="D85" s="44"/>
       <c r="E85" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F85" s="67">
+      <c r="F85" s="52">
         <v>1</v>
       </c>
       <c r="G85" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="H85" s="63"/>
-      <c r="I85" s="63"/>
-      <c r="J85" s="63"/>
-      <c r="K85" s="63">
+      <c r="H85" s="48"/>
+      <c r="I85" s="48"/>
+      <c r="J85" s="48"/>
+      <c r="K85" s="48">
         <v>4</v>
       </c>
-      <c r="L85" s="50">
+      <c r="L85" s="79">
         <v>260</v>
       </c>
       <c r="M85" s="18"/>
@@ -8633,33 +8721,33 @@
         <v>335</v>
       </c>
     </row>
-    <row r="86" spans="1:15" ht="15" customHeight="1">
+    <row r="86" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A86" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B86" s="57" t="s">
+      <c r="B86" s="42" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="55" t="s">
+      <c r="C86" s="40" t="s">
         <v>374</v>
       </c>
-      <c r="D86" s="59"/>
+      <c r="D86" s="44"/>
       <c r="E86" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F86" s="67">
+      <c r="F86" s="52">
         <v>1</v>
       </c>
       <c r="G86" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="H86" s="63"/>
-      <c r="I86" s="63"/>
-      <c r="J86" s="63"/>
-      <c r="K86" s="63">
+      <c r="H86" s="48"/>
+      <c r="I86" s="48"/>
+      <c r="J86" s="48"/>
+      <c r="K86" s="48">
         <v>12</v>
       </c>
-      <c r="L86" s="50">
+      <c r="L86" s="79">
         <v>780</v>
       </c>
       <c r="M86" s="18"/>
@@ -8670,33 +8758,33 @@
         <v>377</v>
       </c>
     </row>
-    <row r="87" spans="1:15" ht="15" customHeight="1">
+    <row r="87" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A87" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B87" s="57" t="s">
+      <c r="B87" s="42" t="s">
         <v>378</v>
       </c>
-      <c r="C87" s="55" t="s">
+      <c r="C87" s="40" t="s">
         <v>379</v>
       </c>
-      <c r="D87" s="59"/>
+      <c r="D87" s="44"/>
       <c r="E87" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F87" s="67">
+      <c r="F87" s="52">
         <v>1</v>
       </c>
       <c r="G87" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="H87" s="63"/>
-      <c r="I87" s="63"/>
-      <c r="J87" s="63"/>
-      <c r="K87" s="63">
+      <c r="H87" s="48"/>
+      <c r="I87" s="48"/>
+      <c r="J87" s="48"/>
+      <c r="K87" s="48">
         <v>12</v>
       </c>
-      <c r="L87" s="50">
+      <c r="L87" s="79">
         <v>780</v>
       </c>
       <c r="M87" s="18"/>
@@ -8707,33 +8795,33 @@
         <v>377</v>
       </c>
     </row>
-    <row r="88" spans="1:15" ht="15" customHeight="1">
+    <row r="88" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A88" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B88" s="57" t="s">
+      <c r="B88" s="42" t="s">
         <v>380</v>
       </c>
-      <c r="C88" s="55" t="s">
+      <c r="C88" s="40" t="s">
         <v>381</v>
       </c>
-      <c r="D88" s="59"/>
+      <c r="D88" s="44"/>
       <c r="E88" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F88" s="67">
+      <c r="F88" s="52">
         <v>1</v>
       </c>
       <c r="G88" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="H88" s="63"/>
-      <c r="I88" s="63"/>
-      <c r="J88" s="63"/>
-      <c r="K88" s="62">
+      <c r="H88" s="48"/>
+      <c r="I88" s="48"/>
+      <c r="J88" s="48"/>
+      <c r="K88" s="47">
         <v>15</v>
       </c>
-      <c r="L88" s="50">
+      <c r="L88" s="79">
         <v>88</v>
       </c>
       <c r="M88" s="18"/>
@@ -8744,33 +8832,33 @@
         <v>383</v>
       </c>
     </row>
-    <row r="89" spans="1:15" ht="15" customHeight="1">
+    <row r="89" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A89" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B89" s="57" t="s">
+      <c r="B89" s="42" t="s">
         <v>384</v>
       </c>
-      <c r="C89" s="55" t="s">
+      <c r="C89" s="40" t="s">
         <v>385</v>
       </c>
-      <c r="D89" s="59"/>
+      <c r="D89" s="44"/>
       <c r="E89" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F89" s="67">
+      <c r="F89" s="52">
         <v>1</v>
       </c>
       <c r="G89" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="H89" s="63"/>
-      <c r="I89" s="63"/>
-      <c r="J89" s="63"/>
-      <c r="K89" s="62">
+      <c r="H89" s="48"/>
+      <c r="I89" s="48"/>
+      <c r="J89" s="48"/>
+      <c r="K89" s="47">
         <v>3</v>
       </c>
-      <c r="L89" s="50">
+      <c r="L89" s="79">
         <v>393</v>
       </c>
       <c r="M89" s="18"/>
@@ -8781,33 +8869,33 @@
         <v>387</v>
       </c>
     </row>
-    <row r="90" spans="1:15" ht="15" customHeight="1">
+    <row r="90" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A90" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B90" s="57" t="s">
+      <c r="B90" s="42" t="s">
         <v>388</v>
       </c>
-      <c r="C90" s="55" t="s">
+      <c r="C90" s="40" t="s">
         <v>389</v>
       </c>
-      <c r="D90" s="59"/>
+      <c r="D90" s="44"/>
       <c r="E90" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F90" s="67">
+      <c r="F90" s="52">
         <v>1</v>
       </c>
       <c r="G90" s="14" t="s">
         <v>390</v>
       </c>
-      <c r="H90" s="63"/>
-      <c r="I90" s="63"/>
-      <c r="J90" s="63"/>
-      <c r="K90" s="62">
-        <v>1</v>
-      </c>
-      <c r="L90" s="50">
+      <c r="H90" s="48"/>
+      <c r="I90" s="48"/>
+      <c r="J90" s="48"/>
+      <c r="K90" s="47">
+        <v>1</v>
+      </c>
+      <c r="L90" s="79">
         <v>102</v>
       </c>
       <c r="M90" s="18"/>
@@ -8818,33 +8906,33 @@
         <v>392</v>
       </c>
     </row>
-    <row r="91" spans="1:15" ht="15" customHeight="1">
+    <row r="91" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A91" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B91" s="57" t="s">
+      <c r="B91" s="42" t="s">
         <v>393</v>
       </c>
-      <c r="C91" s="55" t="s">
+      <c r="C91" s="40" t="s">
         <v>394</v>
       </c>
-      <c r="D91" s="59"/>
+      <c r="D91" s="44"/>
       <c r="E91" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F91" s="67">
+      <c r="F91" s="52">
         <v>1</v>
       </c>
       <c r="G91" s="14" t="s">
         <v>395</v>
       </c>
-      <c r="H91" s="63"/>
-      <c r="I91" s="63"/>
-      <c r="J91" s="63"/>
-      <c r="K91" s="62">
+      <c r="H91" s="48"/>
+      <c r="I91" s="48"/>
+      <c r="J91" s="48"/>
+      <c r="K91" s="47">
         <v>6</v>
       </c>
-      <c r="L91" s="50">
+      <c r="L91" s="79">
         <v>257</v>
       </c>
       <c r="M91" s="18"/>
@@ -8855,33 +8943,33 @@
         <v>396</v>
       </c>
     </row>
-    <row r="92" spans="1:15" ht="15" customHeight="1">
+    <row r="92" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A92" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B92" s="57" t="s">
+      <c r="B92" s="42" t="s">
         <v>397</v>
       </c>
-      <c r="C92" s="55" t="s">
+      <c r="C92" s="40" t="s">
         <v>398</v>
       </c>
-      <c r="D92" s="59"/>
+      <c r="D92" s="44"/>
       <c r="E92" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F92" s="67">
+      <c r="F92" s="52">
         <v>1</v>
       </c>
       <c r="G92" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="H92" s="63"/>
-      <c r="I92" s="63"/>
-      <c r="J92" s="63"/>
-      <c r="K92" s="62">
-        <v>1</v>
-      </c>
-      <c r="L92" s="50">
+      <c r="H92" s="48"/>
+      <c r="I92" s="48"/>
+      <c r="J92" s="48"/>
+      <c r="K92" s="47">
+        <v>1</v>
+      </c>
+      <c r="L92" s="79">
         <v>63</v>
       </c>
       <c r="M92" s="18"/>
@@ -8892,33 +8980,33 @@
         <v>313</v>
       </c>
     </row>
-    <row r="93" spans="1:15" ht="15" customHeight="1">
+    <row r="93" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A93" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B93" s="57" t="s">
+      <c r="B93" s="42" t="s">
         <v>399</v>
       </c>
-      <c r="C93" s="55" t="s">
+      <c r="C93" s="40" t="s">
         <v>400</v>
       </c>
-      <c r="D93" s="59"/>
+      <c r="D93" s="44"/>
       <c r="E93" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F93" s="67">
+      <c r="F93" s="52">
         <v>1</v>
       </c>
       <c r="G93" s="14" t="s">
         <v>401</v>
       </c>
-      <c r="H93" s="63"/>
-      <c r="I93" s="63"/>
-      <c r="J93" s="63"/>
-      <c r="K93" s="62">
+      <c r="H93" s="48"/>
+      <c r="I93" s="48"/>
+      <c r="J93" s="48"/>
+      <c r="K93" s="47">
         <v>5</v>
       </c>
-      <c r="L93" s="50">
+      <c r="L93" s="79">
         <v>22.8</v>
       </c>
       <c r="M93" s="18"/>
@@ -8929,33 +9017,33 @@
         <v>315</v>
       </c>
     </row>
-    <row r="94" spans="1:15" ht="15" customHeight="1">
+    <row r="94" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A94" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B94" s="57" t="s">
+      <c r="B94" s="42" t="s">
         <v>403</v>
       </c>
-      <c r="C94" s="55" t="s">
+      <c r="C94" s="40" t="s">
         <v>404</v>
       </c>
-      <c r="D94" s="59"/>
+      <c r="D94" s="44"/>
       <c r="E94" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F94" s="67">
+      <c r="F94" s="52">
         <v>1</v>
       </c>
       <c r="G94" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="H94" s="63"/>
-      <c r="I94" s="63"/>
-      <c r="J94" s="63"/>
-      <c r="K94" s="62">
+      <c r="H94" s="48"/>
+      <c r="I94" s="48"/>
+      <c r="J94" s="48"/>
+      <c r="K94" s="47">
         <v>2</v>
       </c>
-      <c r="L94" s="50">
+      <c r="L94" s="79">
         <v>25</v>
       </c>
       <c r="M94" s="18"/>
@@ -8966,33 +9054,33 @@
         <v>406</v>
       </c>
     </row>
-    <row r="95" spans="1:15" ht="15" customHeight="1">
+    <row r="95" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A95" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B95" s="57" t="s">
+      <c r="B95" s="42" t="s">
         <v>407</v>
       </c>
-      <c r="C95" s="55" t="s">
+      <c r="C95" s="40" t="s">
         <v>408</v>
       </c>
-      <c r="D95" s="59"/>
+      <c r="D95" s="44"/>
       <c r="E95" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F95" s="67">
+      <c r="F95" s="52">
         <v>1</v>
       </c>
       <c r="G95" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="H95" s="63"/>
-      <c r="I95" s="63"/>
-      <c r="J95" s="63"/>
-      <c r="K95" s="62">
+      <c r="H95" s="48"/>
+      <c r="I95" s="48"/>
+      <c r="J95" s="48"/>
+      <c r="K95" s="47">
         <v>2</v>
       </c>
-      <c r="L95" s="50">
+      <c r="L95" s="79">
         <v>270</v>
       </c>
       <c r="M95" s="18"/>
@@ -9003,33 +9091,33 @@
         <v>324</v>
       </c>
     </row>
-    <row r="96" spans="1:15" ht="15" customHeight="1">
+    <row r="96" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A96" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B96" s="57" t="s">
+      <c r="B96" s="42" t="s">
         <v>409</v>
       </c>
-      <c r="C96" s="55" t="s">
+      <c r="C96" s="40" t="s">
         <v>410</v>
       </c>
-      <c r="D96" s="59"/>
+      <c r="D96" s="44"/>
       <c r="E96" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F96" s="67">
+      <c r="F96" s="52">
         <v>1</v>
       </c>
       <c r="G96" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="H96" s="63"/>
-      <c r="I96" s="63"/>
-      <c r="J96" s="63"/>
-      <c r="K96" s="62">
-        <v>1</v>
-      </c>
-      <c r="L96" s="50">
+      <c r="H96" s="48"/>
+      <c r="I96" s="48"/>
+      <c r="J96" s="48"/>
+      <c r="K96" s="47">
+        <v>1</v>
+      </c>
+      <c r="L96" s="79">
         <v>18.5</v>
       </c>
       <c r="M96" s="18"/>
@@ -9040,33 +9128,33 @@
         <v>327</v>
       </c>
     </row>
-    <row r="97" spans="1:15" ht="15" customHeight="1">
+    <row r="97" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A97" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B97" s="57" t="s">
+      <c r="B97" s="42" t="s">
         <v>411</v>
       </c>
-      <c r="C97" s="55" t="s">
+      <c r="C97" s="40" t="s">
         <v>412</v>
       </c>
-      <c r="D97" s="59"/>
+      <c r="D97" s="44"/>
       <c r="E97" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F97" s="67">
+      <c r="F97" s="52">
         <v>1</v>
       </c>
       <c r="G97" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="H97" s="63"/>
-      <c r="I97" s="63"/>
-      <c r="J97" s="63"/>
-      <c r="K97" s="62">
+      <c r="H97" s="48"/>
+      <c r="I97" s="48"/>
+      <c r="J97" s="48"/>
+      <c r="K97" s="47">
         <v>2</v>
       </c>
-      <c r="L97" s="50">
+      <c r="L97" s="79">
         <v>84.5</v>
       </c>
       <c r="M97" s="18"/>
@@ -9077,33 +9165,33 @@
         <v>329</v>
       </c>
     </row>
-    <row r="98" spans="1:15" ht="15" customHeight="1">
+    <row r="98" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A98" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B98" s="57" t="s">
+      <c r="B98" s="42" t="s">
         <v>413</v>
       </c>
-      <c r="C98" s="55" t="s">
+      <c r="C98" s="40" t="s">
         <v>414</v>
       </c>
-      <c r="D98" s="59"/>
+      <c r="D98" s="44"/>
       <c r="E98" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F98" s="67">
+      <c r="F98" s="52">
         <v>1</v>
       </c>
       <c r="G98" s="14" t="s">
         <v>415</v>
       </c>
-      <c r="H98" s="63"/>
-      <c r="I98" s="63"/>
-      <c r="J98" s="63"/>
-      <c r="K98" s="62">
+      <c r="H98" s="48"/>
+      <c r="I98" s="48"/>
+      <c r="J98" s="48"/>
+      <c r="K98" s="47">
         <v>10</v>
       </c>
-      <c r="L98" s="50">
+      <c r="L98" s="79">
         <v>63</v>
       </c>
       <c r="M98" s="18"/>
@@ -9114,33 +9202,33 @@
         <v>332</v>
       </c>
     </row>
-    <row r="99" spans="1:15" ht="15" customHeight="1">
+    <row r="99" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A99" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B99" s="57" t="s">
+      <c r="B99" s="42" t="s">
         <v>417</v>
       </c>
-      <c r="C99" s="55" t="s">
+      <c r="C99" s="40" t="s">
         <v>418</v>
       </c>
-      <c r="D99" s="59"/>
+      <c r="D99" s="44"/>
       <c r="E99" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F99" s="67">
+      <c r="F99" s="52">
         <v>1</v>
       </c>
       <c r="G99" s="14" t="s">
         <v>419</v>
       </c>
-      <c r="H99" s="63"/>
-      <c r="I99" s="63"/>
-      <c r="J99" s="63"/>
-      <c r="K99" s="62">
+      <c r="H99" s="48"/>
+      <c r="I99" s="48"/>
+      <c r="J99" s="48"/>
+      <c r="K99" s="47">
         <v>5</v>
       </c>
-      <c r="L99" s="50">
+      <c r="L99" s="79">
         <v>33</v>
       </c>
       <c r="M99" s="18"/>
@@ -9151,33 +9239,33 @@
         <v>420</v>
       </c>
     </row>
-    <row r="100" spans="1:15" ht="15" customHeight="1">
+    <row r="100" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A100" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B100" s="57" t="s">
+      <c r="B100" s="42" t="s">
         <v>421</v>
       </c>
-      <c r="C100" s="55" t="s">
+      <c r="C100" s="40" t="s">
         <v>422</v>
       </c>
-      <c r="D100" s="59"/>
+      <c r="D100" s="44"/>
       <c r="E100" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F100" s="67">
+      <c r="F100" s="52">
         <v>1</v>
       </c>
       <c r="G100" s="14" t="s">
         <v>344</v>
       </c>
-      <c r="H100" s="63"/>
-      <c r="I100" s="63"/>
-      <c r="J100" s="63"/>
-      <c r="K100" s="62">
-        <v>1</v>
-      </c>
-      <c r="L100" s="50">
+      <c r="H100" s="48"/>
+      <c r="I100" s="48"/>
+      <c r="J100" s="48"/>
+      <c r="K100" s="47">
+        <v>1</v>
+      </c>
+      <c r="L100" s="79">
         <v>19</v>
       </c>
       <c r="M100" s="18"/>
@@ -9188,33 +9276,33 @@
         <v>345</v>
       </c>
     </row>
-    <row r="101" spans="1:15" ht="15" customHeight="1">
+    <row r="101" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A101" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B101" s="57" t="s">
+      <c r="B101" s="42" t="s">
         <v>423</v>
       </c>
-      <c r="C101" s="55" t="s">
+      <c r="C101" s="40" t="s">
         <v>424</v>
       </c>
-      <c r="D101" s="59"/>
+      <c r="D101" s="44"/>
       <c r="E101" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F101" s="67">
+      <c r="F101" s="52">
         <v>1</v>
       </c>
       <c r="G101" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="H101" s="63"/>
-      <c r="I101" s="63"/>
-      <c r="J101" s="63"/>
-      <c r="K101" s="62">
+      <c r="H101" s="48"/>
+      <c r="I101" s="48"/>
+      <c r="J101" s="48"/>
+      <c r="K101" s="47">
         <v>2</v>
       </c>
-      <c r="L101" s="50">
+      <c r="L101" s="79">
         <v>11</v>
       </c>
       <c r="M101" s="18"/>
@@ -9225,33 +9313,33 @@
         <v>427</v>
       </c>
     </row>
-    <row r="102" spans="1:15" ht="24" customHeight="1">
+    <row r="102" spans="1:15" s="43" customFormat="1" ht="24" customHeight="1">
       <c r="A102" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B102" s="57" t="s">
+      <c r="B102" s="42" t="s">
         <v>428</v>
       </c>
-      <c r="C102" s="55" t="s">
+      <c r="C102" s="40" t="s">
         <v>429</v>
       </c>
-      <c r="D102" s="59"/>
+      <c r="D102" s="44"/>
       <c r="E102" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F102" s="67">
+      <c r="F102" s="52">
         <v>1</v>
       </c>
       <c r="G102" s="14" t="s">
         <v>361</v>
       </c>
-      <c r="H102" s="63"/>
-      <c r="I102" s="63"/>
-      <c r="J102" s="63"/>
-      <c r="K102" s="62">
+      <c r="H102" s="48"/>
+      <c r="I102" s="48"/>
+      <c r="J102" s="48"/>
+      <c r="K102" s="47">
         <v>50</v>
       </c>
-      <c r="L102" s="50">
+      <c r="L102" s="79">
         <v>220</v>
       </c>
       <c r="M102" s="18"/>
@@ -9262,33 +9350,33 @@
         <v>294</v>
       </c>
     </row>
-    <row r="103" spans="1:15" ht="15" customHeight="1">
+    <row r="103" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A103" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B103" s="57" t="s">
+      <c r="B103" s="42" t="s">
         <v>430</v>
       </c>
-      <c r="C103" s="55" t="s">
+      <c r="C103" s="40" t="s">
         <v>431</v>
       </c>
-      <c r="D103" s="59"/>
+      <c r="D103" s="44"/>
       <c r="E103" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F103" s="67">
+      <c r="F103" s="52">
         <v>1</v>
       </c>
       <c r="G103" s="14" t="s">
         <v>361</v>
       </c>
-      <c r="H103" s="63"/>
-      <c r="I103" s="63"/>
-      <c r="J103" s="63"/>
-      <c r="K103" s="62">
+      <c r="H103" s="48"/>
+      <c r="I103" s="48"/>
+      <c r="J103" s="48"/>
+      <c r="K103" s="47">
         <v>50</v>
       </c>
-      <c r="L103" s="50">
+      <c r="L103" s="79">
         <v>245</v>
       </c>
       <c r="M103" s="18"/>
@@ -9297,33 +9385,33 @@
       </c>
       <c r="O103" s="22"/>
     </row>
-    <row r="104" spans="1:15" ht="15" customHeight="1">
+    <row r="104" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A104" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B104" s="57" t="s">
+      <c r="B104" s="42" t="s">
         <v>432</v>
       </c>
-      <c r="C104" s="55" t="s">
+      <c r="C104" s="40" t="s">
         <v>433</v>
       </c>
-      <c r="D104" s="59"/>
+      <c r="D104" s="44"/>
       <c r="E104" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F104" s="67">
+      <c r="F104" s="52">
         <v>1</v>
       </c>
       <c r="G104" s="14" t="s">
         <v>434</v>
       </c>
-      <c r="H104" s="63"/>
-      <c r="I104" s="63"/>
-      <c r="J104" s="63"/>
-      <c r="K104" s="62">
+      <c r="H104" s="48"/>
+      <c r="I104" s="48"/>
+      <c r="J104" s="48"/>
+      <c r="K104" s="47">
         <v>6</v>
       </c>
-      <c r="L104" s="50">
+      <c r="L104" s="79">
         <v>257</v>
       </c>
       <c r="M104" s="18"/>
@@ -9334,33 +9422,33 @@
         <v>435</v>
       </c>
     </row>
-    <row r="105" spans="1:15" ht="15" customHeight="1">
+    <row r="105" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A105" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B105" s="57" t="s">
+      <c r="B105" s="42" t="s">
         <v>436</v>
       </c>
-      <c r="C105" s="55" t="s">
+      <c r="C105" s="40" t="s">
         <v>437</v>
       </c>
-      <c r="D105" s="59"/>
+      <c r="D105" s="44"/>
       <c r="E105" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F105" s="67">
+      <c r="F105" s="52">
         <v>1</v>
       </c>
       <c r="G105" s="14" t="s">
         <v>434</v>
       </c>
-      <c r="H105" s="63"/>
-      <c r="I105" s="63"/>
-      <c r="J105" s="63"/>
-      <c r="K105" s="62">
+      <c r="H105" s="48"/>
+      <c r="I105" s="48"/>
+      <c r="J105" s="48"/>
+      <c r="K105" s="47">
         <v>6</v>
       </c>
-      <c r="L105" s="50">
+      <c r="L105" s="79">
         <v>428.5</v>
       </c>
       <c r="M105" s="18"/>
@@ -9371,33 +9459,33 @@
         <v>350</v>
       </c>
     </row>
-    <row r="106" spans="1:15" ht="15" customHeight="1">
+    <row r="106" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A106" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B106" s="57" t="s">
+      <c r="B106" s="42" t="s">
         <v>438</v>
       </c>
-      <c r="C106" s="55" t="s">
+      <c r="C106" s="40" t="s">
         <v>439</v>
       </c>
-      <c r="D106" s="59"/>
+      <c r="D106" s="44"/>
       <c r="E106" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F106" s="67">
+      <c r="F106" s="52">
         <v>1</v>
       </c>
       <c r="G106" s="14" t="s">
         <v>434</v>
       </c>
-      <c r="H106" s="63"/>
-      <c r="I106" s="63"/>
-      <c r="J106" s="63"/>
-      <c r="K106" s="62">
+      <c r="H106" s="48"/>
+      <c r="I106" s="48"/>
+      <c r="J106" s="48"/>
+      <c r="K106" s="47">
         <v>6</v>
       </c>
-      <c r="L106" s="50">
+      <c r="L106" s="79">
         <v>90.5</v>
       </c>
       <c r="M106" s="18"/>
@@ -9408,33 +9496,33 @@
         <v>441</v>
       </c>
     </row>
-    <row r="107" spans="1:15" ht="15" customHeight="1">
+    <row r="107" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A107" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B107" s="57" t="s">
+      <c r="B107" s="42" t="s">
         <v>442</v>
       </c>
-      <c r="C107" s="55" t="s">
+      <c r="C107" s="40" t="s">
         <v>443</v>
       </c>
-      <c r="D107" s="59"/>
+      <c r="D107" s="44"/>
       <c r="E107" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F107" s="67">
+      <c r="F107" s="52">
         <v>1</v>
       </c>
       <c r="G107" s="14" t="s">
         <v>444</v>
       </c>
-      <c r="H107" s="63"/>
-      <c r="I107" s="63"/>
-      <c r="J107" s="63"/>
-      <c r="K107" s="62">
+      <c r="H107" s="48"/>
+      <c r="I107" s="48"/>
+      <c r="J107" s="48"/>
+      <c r="K107" s="47">
         <v>2</v>
       </c>
-      <c r="L107" s="50">
+      <c r="L107" s="79">
         <v>7</v>
       </c>
       <c r="M107" s="18"/>
@@ -9445,32 +9533,32 @@
         <v>445</v>
       </c>
     </row>
-    <row r="108" spans="1:15" ht="25.5" customHeight="1">
+    <row r="108" spans="1:15" s="43" customFormat="1" ht="25.5" customHeight="1">
       <c r="A108" s="11" t="s">
         <v>446</v>
       </c>
-      <c r="B108" s="57"/>
-      <c r="C108" s="55" t="s">
+      <c r="B108" s="42"/>
+      <c r="C108" s="40" t="s">
         <v>447</v>
       </c>
-      <c r="D108" s="59"/>
+      <c r="D108" s="44"/>
       <c r="E108" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F108" s="67">
+      <c r="F108" s="52">
         <v>1</v>
       </c>
       <c r="G108" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="H108" s="63"/>
-      <c r="I108" s="63"/>
-      <c r="J108" s="63"/>
-      <c r="K108" s="62">
-        <f t="shared" ref="K67:K113" si="2">SUM(I108*J108)</f>
+      <c r="H108" s="48"/>
+      <c r="I108" s="48"/>
+      <c r="J108" s="48"/>
+      <c r="K108" s="47">
+        <f t="shared" ref="K108:K113" si="2">SUM(I108*J108)</f>
         <v>0</v>
       </c>
-      <c r="L108" s="50">
+      <c r="L108" s="79">
         <v>29.17</v>
       </c>
       <c r="M108" s="18"/>
@@ -9479,92 +9567,92 @@
         <v>449</v>
       </c>
     </row>
-    <row r="109" spans="1:15" ht="25.5" customHeight="1">
+    <row r="109" spans="1:15" s="43" customFormat="1" ht="25.5" customHeight="1">
       <c r="A109" s="11" t="s">
         <v>446</v>
       </c>
-      <c r="B109" s="57"/>
-      <c r="C109" s="55" t="s">
+      <c r="B109" s="42"/>
+      <c r="C109" s="40" t="s">
         <v>450</v>
       </c>
-      <c r="D109" s="59"/>
+      <c r="D109" s="44"/>
       <c r="E109" s="11"/>
-      <c r="F109" s="67">
+      <c r="F109" s="52">
         <v>1</v>
       </c>
       <c r="G109" s="14" t="s">
         <v>451</v>
       </c>
-      <c r="H109" s="63"/>
-      <c r="I109" s="63"/>
-      <c r="J109" s="63"/>
-      <c r="K109" s="62">
+      <c r="H109" s="48"/>
+      <c r="I109" s="48"/>
+      <c r="J109" s="48"/>
+      <c r="K109" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L109" s="50"/>
+      <c r="L109" s="79"/>
       <c r="M109" s="18"/>
       <c r="N109" s="18"/>
       <c r="O109" s="22" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="110" spans="1:15" ht="25.5" customHeight="1">
+    <row r="110" spans="1:15" s="43" customFormat="1" ht="25.5" customHeight="1">
       <c r="A110" s="11" t="s">
         <v>446</v>
       </c>
-      <c r="B110" s="57"/>
-      <c r="C110" s="55" t="s">
+      <c r="B110" s="42"/>
+      <c r="C110" s="40" t="s">
         <v>453</v>
       </c>
-      <c r="D110" s="59"/>
+      <c r="D110" s="44"/>
       <c r="E110" s="11"/>
-      <c r="F110" s="67">
+      <c r="F110" s="52">
         <v>1</v>
       </c>
       <c r="G110" s="14" t="s">
         <v>454</v>
       </c>
-      <c r="H110" s="63"/>
-      <c r="I110" s="63"/>
-      <c r="J110" s="63"/>
-      <c r="K110" s="62">
+      <c r="H110" s="48"/>
+      <c r="I110" s="48"/>
+      <c r="J110" s="48"/>
+      <c r="K110" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L110" s="50"/>
+      <c r="L110" s="79"/>
       <c r="M110" s="18"/>
       <c r="N110" s="18"/>
       <c r="O110" s="22" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="111" spans="1:15" ht="15" customHeight="1">
+    <row r="111" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A111" s="11" t="s">
         <v>446</v>
       </c>
-      <c r="B111" s="57"/>
-      <c r="C111" s="55" t="s">
+      <c r="B111" s="42"/>
+      <c r="C111" s="40" t="s">
         <v>456</v>
       </c>
-      <c r="D111" s="59"/>
+      <c r="D111" s="44"/>
       <c r="E111" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F111" s="67">
+      <c r="F111" s="52">
         <v>1</v>
       </c>
       <c r="G111" s="14" t="s">
         <v>457</v>
       </c>
-      <c r="H111" s="63"/>
-      <c r="I111" s="63"/>
-      <c r="J111" s="63"/>
-      <c r="K111" s="62">
+      <c r="H111" s="48"/>
+      <c r="I111" s="48"/>
+      <c r="J111" s="48"/>
+      <c r="K111" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L111" s="50">
+      <c r="L111" s="79">
         <v>0.14000000000000001</v>
       </c>
       <c r="M111" s="18"/>
@@ -9573,64 +9661,69 @@
         <v>458</v>
       </c>
     </row>
-    <row r="112" spans="1:15" ht="15" customHeight="1">
+    <row r="112" spans="1:15" s="43" customFormat="1" ht="15" customHeight="1">
       <c r="A112" s="11" t="s">
         <v>446</v>
       </c>
-      <c r="B112" s="57"/>
-      <c r="C112" s="55" t="s">
+      <c r="B112" s="42"/>
+      <c r="C112" s="40" t="s">
         <v>459</v>
       </c>
-      <c r="D112" s="59"/>
+      <c r="D112" s="44"/>
       <c r="E112" s="11"/>
-      <c r="F112" s="67">
+      <c r="F112" s="52">
         <v>1</v>
       </c>
       <c r="G112" s="14" t="s">
         <v>460</v>
       </c>
-      <c r="H112" s="63"/>
-      <c r="I112" s="63"/>
-      <c r="J112" s="63"/>
-      <c r="K112" s="62">
+      <c r="H112" s="48"/>
+      <c r="I112" s="48"/>
+      <c r="J112" s="48"/>
+      <c r="K112" s="47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L112" s="50"/>
+      <c r="L112" s="79"/>
       <c r="M112" s="18"/>
       <c r="N112" s="18"/>
       <c r="O112" s="22" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="113" spans="1:15" ht="15" customHeight="1">
-      <c r="A113" s="11" t="s">
+    <row r="113" spans="1:15" s="78" customFormat="1" ht="15" customHeight="1">
+      <c r="A113" s="68" t="s">
         <v>446</v>
       </c>
-      <c r="B113" s="57"/>
-      <c r="C113" s="55" t="s">
+      <c r="B113" s="69"/>
+      <c r="C113" s="70" t="s">
         <v>461</v>
       </c>
-      <c r="D113" s="59"/>
-      <c r="E113" s="11"/>
-      <c r="F113" s="67">
-        <v>1</v>
-      </c>
-      <c r="G113" s="14" t="s">
+      <c r="D113" s="71"/>
+      <c r="E113" s="68"/>
+      <c r="F113" s="72">
+        <v>1</v>
+      </c>
+      <c r="G113" s="73" t="s">
         <v>462</v>
       </c>
-      <c r="H113" s="63"/>
-      <c r="I113" s="63"/>
-      <c r="J113" s="63"/>
-      <c r="K113" s="62">
+      <c r="H113" s="74"/>
+      <c r="I113" s="74"/>
+      <c r="J113" s="74"/>
+      <c r="K113" s="75">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L113" s="50"/>
-      <c r="M113" s="18"/>
-      <c r="N113" s="18"/>
-      <c r="O113" s="22" t="s">
+      <c r="L113" s="80"/>
+      <c r="M113" s="76"/>
+      <c r="N113" s="76"/>
+      <c r="O113" s="77" t="s">
         <v>455</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
+      <c r="L114" s="82">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -9646,41 +9739,41 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H223"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="29.85546875" customWidth="1"/>
+    <col min="3" max="3" width="29.81640625" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="30.140625" customWidth="1"/>
+    <col min="7" max="7" width="15.7265625" customWidth="1"/>
+    <col min="8" max="8" width="30.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
       <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="57" t="s">
         <v>464</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
     </row>
     <row r="3" spans="1:8" ht="27.75" customHeight="1">
       <c r="A3" s="10" t="s">
@@ -9709,16 +9802,16 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="19.5" customHeight="1">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="64" t="s">
         <v>465</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
       <c r="A5" s="11" t="s">
@@ -12117,28 +12210,28 @@
       </c>
     </row>
     <row r="98" spans="1:8" ht="19.5" customHeight="1">
-      <c r="A98" s="47" t="s">
+      <c r="A98" s="65" t="s">
         <v>290</v>
       </c>
-      <c r="B98" s="47"/>
-      <c r="C98" s="47"/>
-      <c r="D98" s="47"/>
-      <c r="E98" s="47"/>
+      <c r="B98" s="65"/>
+      <c r="C98" s="65"/>
+      <c r="D98" s="65"/>
+      <c r="E98" s="65"/>
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
     </row>
     <row r="99" spans="1:8" ht="19.5" customHeight="1">
-      <c r="A99" s="46" t="s">
+      <c r="A99" s="64" t="s">
         <v>809</v>
       </c>
-      <c r="B99" s="46"/>
-      <c r="C99" s="46"/>
-      <c r="D99" s="46"/>
-      <c r="E99" s="46"/>
-      <c r="F99" s="46"/>
-      <c r="G99" s="46"/>
-      <c r="H99" s="46"/>
+      <c r="B99" s="64"/>
+      <c r="C99" s="64"/>
+      <c r="D99" s="64"/>
+      <c r="E99" s="64"/>
+      <c r="F99" s="64"/>
+      <c r="G99" s="64"/>
+      <c r="H99" s="64"/>
     </row>
     <row r="100" spans="1:8" ht="15" customHeight="1">
       <c r="A100" s="11" t="s">
@@ -13341,28 +13434,28 @@
       <c r="H159" s="22"/>
     </row>
     <row r="160" spans="1:8" ht="19.5" customHeight="1">
-      <c r="A160" s="47" t="s">
+      <c r="A160" s="65" t="s">
         <v>357</v>
       </c>
-      <c r="B160" s="47"/>
-      <c r="C160" s="47"/>
-      <c r="D160" s="47"/>
-      <c r="E160" s="47"/>
+      <c r="B160" s="65"/>
+      <c r="C160" s="65"/>
+      <c r="D160" s="65"/>
+      <c r="E160" s="65"/>
       <c r="F160" s="4"/>
       <c r="G160" s="4"/>
       <c r="H160" s="4"/>
     </row>
     <row r="161" spans="1:8" ht="19.5" customHeight="1">
-      <c r="A161" s="46" t="s">
+      <c r="A161" s="64" t="s">
         <v>876</v>
       </c>
-      <c r="B161" s="46"/>
-      <c r="C161" s="46"/>
-      <c r="D161" s="46"/>
-      <c r="E161" s="46"/>
-      <c r="F161" s="46"/>
-      <c r="G161" s="46"/>
-      <c r="H161" s="46"/>
+      <c r="B161" s="64"/>
+      <c r="C161" s="64"/>
+      <c r="D161" s="64"/>
+      <c r="E161" s="64"/>
+      <c r="F161" s="64"/>
+      <c r="G161" s="64"/>
+      <c r="H161" s="64"/>
     </row>
     <row r="162" spans="1:8" ht="36" customHeight="1">
       <c r="A162" s="11" t="s">
@@ -14391,16 +14484,16 @@
       </c>
     </row>
     <row r="205" spans="1:8" ht="19.5" hidden="1" customHeight="1">
-      <c r="A205" s="46" t="s">
+      <c r="A205" s="64" t="s">
         <v>992</v>
       </c>
-      <c r="B205" s="46"/>
-      <c r="C205" s="46"/>
-      <c r="D205" s="46"/>
-      <c r="E205" s="46"/>
-      <c r="F205" s="46"/>
-      <c r="G205" s="46"/>
-      <c r="H205" s="46"/>
+      <c r="B205" s="64"/>
+      <c r="C205" s="64"/>
+      <c r="D205" s="64"/>
+      <c r="E205" s="64"/>
+      <c r="F205" s="64"/>
+      <c r="G205" s="64"/>
+      <c r="H205" s="64"/>
     </row>
     <row r="206" spans="1:8" ht="39" hidden="1" customHeight="1">
       <c r="A206" s="11" t="s">
@@ -14727,25 +14820,25 @@
       </c>
     </row>
     <row r="221" spans="1:8" ht="19.5" hidden="1" customHeight="1">
-      <c r="A221" s="47" t="s">
+      <c r="A221" s="65" t="s">
         <v>463</v>
       </c>
-      <c r="B221" s="47"/>
-      <c r="C221" s="47"/>
-      <c r="D221" s="47"/>
-      <c r="E221" s="47"/>
+      <c r="B221" s="65"/>
+      <c r="C221" s="65"/>
+      <c r="D221" s="65"/>
+      <c r="E221" s="65"/>
       <c r="F221" s="4"/>
       <c r="G221" s="4"/>
       <c r="H221" s="4"/>
     </row>
     <row r="222" spans="1:8" ht="19.5" hidden="1" customHeight="1">
-      <c r="A222" s="48" t="s">
+      <c r="A222" s="66" t="s">
         <v>1030</v>
       </c>
-      <c r="B222" s="48"/>
-      <c r="C222" s="48"/>
-      <c r="D222" s="48"/>
-      <c r="E222" s="48"/>
+      <c r="B222" s="66"/>
+      <c r="C222" s="66"/>
+      <c r="D222" s="66"/>
+      <c r="E222" s="66"/>
       <c r="F222" s="24"/>
       <c r="G222" s="24"/>
       <c r="H222" s="24"/>
@@ -14753,16 +14846,16 @@
     <row r="223" spans="1:8" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A222:E222"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A99:H99"/>
+    <mergeCell ref="A160:E160"/>
+    <mergeCell ref="A161:H161"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A205:H205"/>
     <mergeCell ref="A221:E221"/>
-    <mergeCell ref="A222:E222"/>
-    <mergeCell ref="A98:E98"/>
-    <mergeCell ref="A99:H99"/>
-    <mergeCell ref="A160:E160"/>
-    <mergeCell ref="A161:H161"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.5"/>
@@ -14776,7 +14869,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -14791,54 +14884,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="L1" s="43"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="56"/>
     </row>
     <row r="2" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="57" t="s">
         <v>1031</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="58" t="s">
         <v>1032</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="27.75" customHeight="1">
       <c r="A5" s="10" t="s">
@@ -14879,20 +14972,20 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="64" t="s">
         <v>1040</v>
       </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
     </row>
     <row r="7" spans="1:12" ht="25.5" customHeight="1">
       <c r="A7" s="11" t="s">
@@ -15177,17 +15270,17 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A15" s="47" t="s">
+      <c r="A15" s="65" t="s">
         <v>290</v>
       </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="65"/>
       <c r="J15" s="19">
         <f>SUM(J7:J14)</f>
         <v>17083.400000000001</v>
@@ -15196,35 +15289,35 @@
       <c r="L15" s="4"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1">
-      <c r="A16" s="49" t="s">
+      <c r="A16" s="67" t="s">
         <v>1067</v>
       </c>
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="49"/>
+      <c r="B16" s="67"/>
+      <c r="C16" s="67"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="67"/>
       <c r="H16" s="35">
         <f>SUM(H7:H14)</f>
         <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A17" s="46" t="s">
+      <c r="A17" s="64" t="s">
         <v>1068</v>
       </c>
-      <c r="B17" s="46"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="46"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="64"/>
+      <c r="G17" s="64"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="64"/>
+      <c r="K17" s="64"/>
+      <c r="L17" s="64"/>
     </row>
     <row r="18" spans="1:12" ht="24" customHeight="1">
       <c r="A18" s="11" t="s">
@@ -15265,17 +15358,17 @@
       </c>
     </row>
     <row r="19" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="65" t="s">
         <v>1073</v>
       </c>
-      <c r="B19" s="47"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="65"/>
       <c r="J19" s="19">
         <f>SUM(J18)</f>
         <v>343</v>
@@ -15284,20 +15377,20 @@
       <c r="L19" s="4"/>
     </row>
     <row r="20" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A20" s="46" t="s">
+      <c r="A20" s="64" t="s">
         <v>1074</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="46"/>
+      <c r="B20" s="64"/>
+      <c r="C20" s="64"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="64"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="64"/>
+      <c r="K20" s="64"/>
+      <c r="L20" s="64"/>
     </row>
     <row r="21" spans="1:12" ht="24" customHeight="1">
       <c r="A21" s="11" t="s">
@@ -15336,17 +15429,17 @@
       </c>
     </row>
     <row r="22" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="65" t="s">
         <v>1077</v>
       </c>
-      <c r="B22" s="47"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="65"/>
       <c r="J22" s="19">
         <f>SUM(J21)</f>
         <v>90.27</v>
@@ -15355,20 +15448,20 @@
       <c r="L22" s="4"/>
     </row>
     <row r="23" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A23" s="46" t="s">
+      <c r="A23" s="64" t="s">
         <v>1078</v>
       </c>
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46"/>
+      <c r="B23" s="64"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="64"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="64"/>
+      <c r="J23" s="64"/>
+      <c r="K23" s="64"/>
+      <c r="L23" s="64"/>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1">
       <c r="A24" s="11" t="s">
@@ -15491,17 +15584,17 @@
       </c>
     </row>
     <row r="28" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A28" s="47" t="s">
+      <c r="A28" s="65" t="s">
         <v>463</v>
       </c>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="47"/>
+      <c r="B28" s="65"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="65"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="65"/>
+      <c r="H28" s="65"/>
+      <c r="I28" s="65"/>
       <c r="J28" s="19">
         <f>SUM(J24:J27)</f>
         <v>0</v>
@@ -15510,17 +15603,17 @@
       <c r="L28" s="4"/>
     </row>
     <row r="29" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A29" s="48" t="s">
+      <c r="A29" s="66" t="s">
         <v>1087</v>
       </c>
-      <c r="B29" s="48"/>
-      <c r="C29" s="48"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="48"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="48"/>
+      <c r="B29" s="66"/>
+      <c r="C29" s="66"/>
+      <c r="D29" s="66"/>
+      <c r="E29" s="66"/>
+      <c r="F29" s="66"/>
+      <c r="G29" s="66"/>
+      <c r="H29" s="66"/>
+      <c r="I29" s="66"/>
       <c r="J29" s="23">
         <f>J15+J19+J22+J28</f>
         <v>17516.670000000002</v>
@@ -15530,11 +15623,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A6:L6"/>
     <mergeCell ref="A22:I22"/>
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A28:I28"/>
@@ -15544,6 +15632,11 @@
     <mergeCell ref="A17:L17"/>
     <mergeCell ref="A19:I19"/>
     <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A6:L6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.5"/>
